--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46238.17255310185</v>
+        <v>46239.199784502314</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
@@ -2542,8 +2542,8 @@
       <c r="R10" s="5">
         <v>46234</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>33</v>
+      <c r="S10" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46238.17255559028</v>
+        <v>46239.19978417824</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2652,8 +2652,8 @@
       <c r="R12" s="5">
         <v>46234</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>33</v>
+      <c r="S12" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46237.55062730324</v>
+        <v>46240.17126099537</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -3035,7 +3035,7 @@
         <v>46233.90772484954</v>
       </c>
       <c r="D19" s="9">
-        <v>46233.90774027778</v>
+        <v>46240.17731082176</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>44</v>
@@ -3079,8 +3079,8 @@
       <c r="R19" s="9">
         <v>46238</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>33</v>
+      <c r="S19" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46233.65425658565</v>
+        <v>46240.17126667824</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>260</v>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46233.65425313657</v>
+        <v>46240.17126537037</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>263</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="483">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46233.65166045139</v>
+        <v>46240.823460775464</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>75</v>
@@ -3567,9 +3567,11 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I28" s="5">
         <v>46280</v>
       </c>
@@ -3609,7 +3611,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46233.65193393518</v>
+        <v>46240.82345635416</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>105</v>
@@ -3618,9 +3620,11 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="10"/>
+        <v>82</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>83</v>
+      </c>
       <c r="I29" s="9">
         <v>46282</v>
       </c>
@@ -4725,7 +4729,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46233.64825100695</v>
+        <v>46240.824282256945</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>146</v>
@@ -4734,9 +4738,11 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I49" s="9">
         <v>46356</v>
       </c>
@@ -4776,7 +4782,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46233.648260312504</v>
+        <v>46240.824278125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>146</v>
@@ -4785,9 +4791,11 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I50" s="5">
         <v>46356</v>
       </c>
@@ -4827,7 +4835,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46233.64826072917</v>
+        <v>46240.82427431713</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>146</v>
@@ -4836,9 +4844,11 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I51" s="9">
         <v>46356</v>
       </c>
@@ -4878,7 +4888,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46233.64826108796</v>
+        <v>46240.824270625</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>146</v>
@@ -4887,9 +4897,11 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I52" s="5">
         <v>46356</v>
       </c>
@@ -4929,7 +4941,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46233.6482615162</v>
+        <v>46240.824266550924</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>146</v>
@@ -4938,9 +4950,11 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I53" s="9">
         <v>46356</v>
       </c>
@@ -4980,7 +4994,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46233.64826189815</v>
+        <v>46240.82426292824</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>148</v>
@@ -4989,9 +5003,11 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I54" s="5">
         <v>46356</v>
       </c>
@@ -5031,7 +5047,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46233.6482622801</v>
+        <v>46240.824259375004</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>148</v>
@@ -5040,9 +5056,11 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I55" s="9">
         <v>46356</v>
       </c>
@@ -5082,7 +5100,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46233.64826261574</v>
+        <v>46240.824255416665</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>148</v>
@@ -5091,9 +5109,11 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I56" s="5">
         <v>46356</v>
       </c>
@@ -5133,7 +5153,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46233.64826296296</v>
+        <v>46240.8242518287</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>148</v>
@@ -5142,9 +5162,11 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I57" s="9">
         <v>46356</v>
       </c>
@@ -5184,7 +5206,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46233.648263344905</v>
+        <v>46240.824248414356</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>148</v>
@@ -5193,9 +5215,11 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I58" s="5">
         <v>46356</v>
       </c>
@@ -5235,7 +5259,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46233.64826378472</v>
+        <v>46240.82424457176</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>148</v>
@@ -5244,9 +5268,11 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="I59" s="9">
         <v>46356</v>
       </c>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46240.17126099537</v>
+        <v>46241.191987743056</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2715,8 +2715,8 @@
       <c r="R13" s="9">
         <v>46239</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>33</v>
+      <c r="S13" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46240.17126667824</v>
+        <v>46241.191987488426</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>260</v>
@@ -7230,8 +7230,8 @@
       <c r="R94" s="5">
         <v>46239</v>
       </c>
-      <c r="S94" s="7" t="s">
-        <v>33</v>
+      <c r="S94" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46240.17126537037</v>
+        <v>46241.191987488426</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>263</v>
@@ -7293,8 +7293,8 @@
       <c r="R95" s="9">
         <v>46239</v>
       </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
+      <c r="S95" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="485">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -481,25 +481,31 @@
     <t xml:space="preserve">Plano Preliminar  ot 4385- 4386  </t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Plano Definitivos  ot 4385- 4386  ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1217003865116839</t>
+  </si>
+  <si>
+    <t>ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Plano Definitivos  ot 4385- 4386  ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1217003865116839</t>
-  </si>
-  <si>
-    <t>ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1217003865116857</t>
@@ -2498,7 +2504,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46239.199784502314</v>
+        <v>46245.56746402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
@@ -4159,7 +4165,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46238.20052732639</v>
+        <v>46245.568238368054</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -4222,7 +4228,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46233.65254653935</v>
+        <v>46245.17038899305</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4231,10 +4237,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -4268,26 +4274,26 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591185186</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46233.65254203704</v>
+        <v>46245.1703903125</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I41" s="9">
         <v>46239</v>
@@ -4321,17 +4327,17 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83591513889</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46233.65269973379</v>
+        <v>46245.56770357639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4361,10 +4367,10 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="5">
         <v>46274</v>
@@ -4384,7 +4390,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592005787</v>
@@ -4400,10 +4406,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I43" s="9">
         <v>46268</v>
@@ -4421,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>139</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4437,7 +4443,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83592324074</v>
@@ -4447,16 +4453,16 @@
         <v>46233.65265393518</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4474,13 +4480,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4490,7 +4496,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83592622685</v>
@@ -4506,10 +4512,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I45" s="9">
         <v>46275</v>
@@ -4530,10 +4536,10 @@
         <v>136</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="9">
         <v>46275</v>
@@ -4553,7 +4559,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83594578704</v>
@@ -4569,10 +4575,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I46" s="5">
         <v>46275</v>
@@ -4593,7 +4599,7 @@
         <v>64</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>64</v>
@@ -4606,7 +4612,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83594902778</v>
@@ -4616,16 +4622,16 @@
         <v>46233.65294082176</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I47" s="9">
         <v>46275</v>
@@ -4646,7 +4652,7 @@
         <v>64</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>64</v>
@@ -4659,7 +4665,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83595255787</v>
@@ -4669,16 +4675,16 @@
         <v>46233.65334809027</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4699,7 +4705,7 @@
         <v>136</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>136</v>
@@ -4722,7 +4728,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46232.835965266204</v>
@@ -4738,10 +4744,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4759,13 +4765,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4775,7 +4781,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83597435185</v>
@@ -4791,10 +4797,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46356</v>
@@ -4812,13 +4818,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4828,7 +4834,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B51" s="9">
         <v>46232.835996435184</v>
@@ -4844,10 +4850,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I51" s="9">
         <v>46356</v>
@@ -4865,13 +4871,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4881,7 +4887,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83599960648</v>
@@ -4897,10 +4903,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I52" s="5">
         <v>46356</v>
@@ -4918,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4934,7 +4940,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B53" s="9">
         <v>46232.8360029051</v>
@@ -4950,10 +4956,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I53" s="9">
         <v>46356</v>
@@ -4971,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4987,7 +4993,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B54" s="5">
         <v>46232.83600618056</v>
@@ -4997,16 +5003,16 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I54" s="5">
         <v>46356</v>
@@ -5024,13 +5030,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5040,7 +5046,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83600939815</v>
@@ -5050,16 +5056,16 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I55" s="9">
         <v>46356</v>
@@ -5077,13 +5083,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5093,7 +5099,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83601267361</v>
@@ -5103,16 +5109,16 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I56" s="5">
         <v>46356</v>
@@ -5130,13 +5136,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5146,7 +5152,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83601601852</v>
@@ -5156,16 +5162,16 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I57" s="9">
         <v>46356</v>
@@ -5183,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5199,7 +5205,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83601914352</v>
@@ -5209,16 +5215,16 @@
         <v>46240.824248414356</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I58" s="5">
         <v>46356</v>
@@ -5236,13 +5242,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5252,7 +5258,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83602246528</v>
@@ -5262,16 +5268,16 @@
         <v>46240.82424457176</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I59" s="9">
         <v>46356</v>
@@ -5289,13 +5295,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5305,7 +5311,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83611833333</v>
@@ -5315,7 +5321,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5339,7 +5345,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5352,7 +5358,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B61" s="9">
         <v>46232.836122465276</v>
@@ -5362,16 +5368,16 @@
         <v>46233.65395961805</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I61" s="9">
         <v>46293</v>
@@ -5389,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q61" s="9">
         <v>46294</v>
@@ -5415,7 +5421,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83612731482</v>
@@ -5425,16 +5431,16 @@
         <v>46233.65395623843</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46293</v>
@@ -5452,13 +5458,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q62" s="5">
         <v>46294</v>
@@ -5478,7 +5484,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83613222222</v>
@@ -5488,16 +5494,16 @@
         <v>46233.65395206018</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I63" s="9">
         <v>46293</v>
@@ -5515,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>105</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q63" s="9">
         <v>46294</v>
@@ -5541,7 +5547,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836136909726</v>
@@ -5551,7 +5557,7 @@
         <v>46233.65409758102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5578,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q64" s="5">
         <v>46295</v>
@@ -5604,7 +5610,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83614177084</v>
@@ -5614,7 +5620,7 @@
         <v>46233.65408881944</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5641,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q65" s="9">
         <v>46295</v>
@@ -5667,7 +5673,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B66" s="5">
         <v>46232.83614663195</v>
@@ -5677,7 +5683,7 @@
         <v>46233.65408491898</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5704,13 +5710,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q66" s="5">
         <v>46295</v>
@@ -5730,7 +5736,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B67" s="9">
         <v>46232.83615094908</v>
@@ -5740,7 +5746,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5764,7 +5770,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5777,7 +5783,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83615418982</v>
@@ -5793,10 +5799,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46296</v>
@@ -5814,13 +5820,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q68" s="5">
         <v>46304</v>
@@ -5840,7 +5846,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B69" s="9">
         <v>46232.83616251158</v>
@@ -5850,16 +5856,16 @@
         <v>46233.643562094905</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I69" s="9">
         <v>46307</v>
@@ -5877,13 +5883,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q69" s="9">
         <v>46324</v>
@@ -5903,7 +5909,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83616856481</v>
@@ -5919,10 +5925,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I70" s="5">
         <v>46307</v>
@@ -5940,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5956,7 +5962,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B71" s="9">
         <v>46232.83617490741</v>
@@ -5972,10 +5978,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I71" s="9">
         <v>46307</v>
@@ -5993,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6009,7 +6015,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B72" s="5">
         <v>46232.836181412036</v>
@@ -6019,16 +6025,16 @@
         <v>46233.643563680555</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I72" s="5">
         <v>46307</v>
@@ -6046,13 +6052,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6062,7 +6068,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B73" s="9">
         <v>46232.836188587964</v>
@@ -6078,10 +6084,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I73" s="9">
         <v>46307</v>
@@ -6099,13 +6105,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6115,7 +6121,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B74" s="5">
         <v>46232.836193449075</v>
@@ -6131,10 +6137,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I74" s="5">
         <v>46307</v>
@@ -6152,13 +6158,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6168,7 +6174,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B75" s="9">
         <v>46232.83619825232</v>
@@ -6178,16 +6184,16 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I75" s="9">
         <v>46307</v>
@@ -6205,13 +6211,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6221,7 +6227,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B76" s="5">
         <v>46232.8362028125</v>
@@ -6231,16 +6237,16 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46307</v>
@@ -6258,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6274,7 +6280,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B77" s="9">
         <v>46232.83620730324</v>
@@ -6284,16 +6290,16 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I77" s="9">
         <v>46307</v>
@@ -6311,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6327,7 +6333,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B78" s="5">
         <v>46232.83621217593</v>
@@ -6337,16 +6343,16 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I78" s="5">
         <v>46307</v>
@@ -6364,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6380,7 +6386,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B79" s="9">
         <v>46232.8362174537</v>
@@ -6390,16 +6396,16 @@
         <v>46233.64356818287</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I79" s="9">
         <v>46307</v>
@@ -6417,13 +6423,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6433,7 +6439,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B80" s="5">
         <v>46232.836222025464</v>
@@ -6443,16 +6449,16 @@
         <v>46233.64356881945</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I80" s="5">
         <v>46307</v>
@@ -6470,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6486,7 +6492,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B81" s="9">
         <v>46232.836342152776</v>
@@ -6496,7 +6502,7 @@
         <v>46233.64375841436</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6523,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q81" s="9">
         <v>46328</v>
@@ -6549,7 +6555,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B82" s="5">
         <v>46232.83634841435</v>
@@ -6586,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6602,7 +6608,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B83" s="9">
         <v>46232.836353125</v>
@@ -6639,13 +6645,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6655,7 +6661,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B84" s="5">
         <v>46232.836358113425</v>
@@ -6665,7 +6671,7 @@
         <v>46233.643860972225</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6692,13 +6698,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6708,7 +6714,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B85" s="9">
         <v>46232.83636347222</v>
@@ -6745,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6761,7 +6767,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B86" s="5">
         <v>46232.8363674537</v>
@@ -6798,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6814,7 +6820,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B87" s="9">
         <v>46232.83637209491</v>
@@ -6824,7 +6830,7 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6851,13 +6857,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6867,7 +6873,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B88" s="5">
         <v>46232.836376666666</v>
@@ -6877,7 +6883,7 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6904,13 +6910,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6920,7 +6926,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B89" s="9">
         <v>46232.836381319445</v>
@@ -6930,7 +6936,7 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6957,13 +6963,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6973,7 +6979,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B90" s="5">
         <v>46232.83638501157</v>
@@ -6983,7 +6989,7 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7010,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7026,7 +7032,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B91" s="9">
         <v>46232.83638946759</v>
@@ -7036,7 +7042,7 @@
         <v>46233.64385625</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7063,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7079,7 +7085,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B92" s="5">
         <v>46232.836394108796</v>
@@ -7089,7 +7095,7 @@
         <v>46233.64382548611</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7116,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7132,7 +7138,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B93" s="9">
         <v>46232.836502499995</v>
@@ -7142,7 +7148,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -7166,7 +7172,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -7179,7 +7185,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B94" s="5">
         <v>46232.83650636574</v>
@@ -7189,16 +7195,16 @@
         <v>46241.191987488426</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I94" s="5">
         <v>46239</v>
@@ -7216,13 +7222,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q94" s="5">
         <v>46240</v>
@@ -7242,7 +7248,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B95" s="9">
         <v>46232.836519247685</v>
@@ -7252,16 +7258,16 @@
         <v>46241.191987488426</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I95" s="9">
         <v>46239</v>
@@ -7279,13 +7285,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q95" s="9">
         <v>46240</v>
@@ -7305,7 +7311,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B96" s="5">
         <v>46232.83652788194</v>
@@ -7315,16 +7321,16 @@
         <v>46233.65424876157</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I96" s="5">
         <v>46343</v>
@@ -7342,13 +7348,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>131</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q96" s="5">
         <v>46344</v>
@@ -7368,7 +7374,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B97" s="9">
         <v>46232.83654054398</v>
@@ -7378,7 +7384,7 @@
         <v>46233.645743333334</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>25</v>
@@ -7402,7 +7408,7 @@
         <v>26</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>26</v>
@@ -7415,7 +7421,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B98" s="5">
         <v>46232.83654375</v>
@@ -7425,7 +7431,7 @@
         <v>46233.65439393518</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7452,13 +7458,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q98" s="5">
         <v>46346</v>
@@ -7478,7 +7484,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B99" s="9">
         <v>46232.83655042824</v>
@@ -7515,13 +7521,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7531,7 +7537,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B100" s="5">
         <v>46232.836554814814</v>
@@ -7568,13 +7574,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7584,7 +7590,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B101" s="9">
         <v>46232.836558854164</v>
@@ -7621,13 +7627,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7637,7 +7643,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B102" s="5">
         <v>46232.83656295139</v>
@@ -7674,13 +7680,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7690,7 +7696,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B103" s="9">
         <v>46232.83656672454</v>
@@ -7727,13 +7733,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7743,7 +7749,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B104" s="5">
         <v>46232.836570162035</v>
@@ -7753,7 +7759,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7780,13 +7786,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7796,7 +7802,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46232.83657339121</v>
@@ -7806,7 +7812,7 @@
         <v>46233.65449810185</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7833,13 +7839,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7849,7 +7855,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46232.83657665509</v>
@@ -7859,7 +7865,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7886,13 +7892,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7902,7 +7908,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B107" s="9">
         <v>46232.83658011574</v>
@@ -7912,7 +7918,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7939,13 +7945,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7955,7 +7961,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B108" s="5">
         <v>46232.83658361111</v>
@@ -7965,7 +7971,7 @@
         <v>46233.654487141204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7992,13 +7998,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8008,7 +8014,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B109" s="9">
         <v>46232.83658716435</v>
@@ -8018,7 +8024,7 @@
         <v>46233.65448212963</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8045,13 +8051,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8061,7 +8067,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B110" s="5">
         <v>46232.83664298611</v>
@@ -8071,7 +8077,7 @@
         <v>46233.65438969908</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8098,13 +8104,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q110" s="5">
         <v>46349</v>
@@ -8124,7 +8130,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B111" s="9">
         <v>46232.836698935185</v>
@@ -8161,13 +8167,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8177,7 +8183,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B112" s="5">
         <v>46232.83670696759</v>
@@ -8214,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8230,7 +8236,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B113" s="9">
         <v>46232.836713020835</v>
@@ -8267,13 +8273,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8283,7 +8289,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B114" s="5">
         <v>46232.83671971065</v>
@@ -8320,13 +8326,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O114" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="P114" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>300</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8336,7 +8342,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B115" s="9">
         <v>46232.83672694444</v>
@@ -8373,13 +8379,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8389,7 +8395,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B116" s="5">
         <v>46232.8367334375</v>
@@ -8399,7 +8405,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8426,13 +8432,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8442,7 +8448,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B117" s="9">
         <v>46232.83673865741</v>
@@ -8452,7 +8458,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8479,13 +8485,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8495,7 +8501,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B118" s="5">
         <v>46232.83674337963</v>
@@ -8505,7 +8511,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8532,13 +8538,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8548,7 +8554,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B119" s="9">
         <v>46232.83674840278</v>
@@ -8558,7 +8564,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8585,13 +8591,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8601,7 +8607,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B120" s="5">
         <v>46232.83675357639</v>
@@ -8611,7 +8617,7 @@
         <v>46233.65463991898</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8638,13 +8644,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8654,7 +8660,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B121" s="9">
         <v>46232.83675886574</v>
@@ -8664,7 +8670,7 @@
         <v>46233.65463564815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8691,13 +8697,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8707,7 +8713,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B122" s="5">
         <v>46232.836891377316</v>
@@ -8717,7 +8723,7 @@
         <v>46233.65438556713</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8744,13 +8750,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q122" s="5">
         <v>46350</v>
@@ -8770,7 +8776,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B123" s="9">
         <v>46232.83690123842</v>
@@ -8807,13 +8813,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8823,7 +8829,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B124" s="5">
         <v>46232.83690674769</v>
@@ -8860,13 +8866,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8876,7 +8882,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B125" s="9">
         <v>46232.836911527775</v>
@@ -8913,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8929,7 +8935,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B126" s="5">
         <v>46232.836916238426</v>
@@ -8966,13 +8972,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8982,7 +8988,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B127" s="9">
         <v>46232.83692087963</v>
@@ -9019,13 +9025,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9035,7 +9041,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B128" s="5">
         <v>46232.836924375</v>
@@ -9045,7 +9051,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9072,13 +9078,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9088,7 +9094,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B129" s="9">
         <v>46232.836927488424</v>
@@ -9098,7 +9104,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9125,13 +9131,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9141,7 +9147,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B130" s="5">
         <v>46232.836930474536</v>
@@ -9151,7 +9157,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9178,13 +9184,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9194,7 +9200,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B131" s="9">
         <v>46232.836933530096</v>
@@ -9204,7 +9210,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9231,13 +9237,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9247,7 +9253,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B132" s="5">
         <v>46232.83693686343</v>
@@ -9257,7 +9263,7 @@
         <v>46233.65477483797</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9284,13 +9290,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9300,7 +9306,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B133" s="9">
         <v>46232.83694028935</v>
@@ -9310,7 +9316,7 @@
         <v>46233.65477001158</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9337,13 +9343,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9353,7 +9359,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B134" s="5">
         <v>46232.836990428244</v>
@@ -9363,7 +9369,7 @@
         <v>46233.65438166667</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9390,13 +9396,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q134" s="5">
         <v>46351</v>
@@ -9416,7 +9422,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B135" s="9">
         <v>46232.837003043984</v>
@@ -9453,13 +9459,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9469,7 +9475,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5">
         <v>46232.837007395836</v>
@@ -9506,13 +9512,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9522,7 +9528,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B137" s="9">
         <v>46232.83701138889</v>
@@ -9532,7 +9538,7 @@
         <v>46233.655246504626</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9559,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9575,7 +9581,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B138" s="5">
         <v>46232.83701560185</v>
@@ -9585,7 +9591,7 @@
         <v>46233.655243506946</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9612,13 +9618,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9628,7 +9634,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B139" s="9">
         <v>46232.83701969907</v>
@@ -9665,13 +9671,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9681,7 +9687,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B140" s="5">
         <v>46232.83702368056</v>
@@ -9691,7 +9697,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9718,13 +9724,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9734,7 +9740,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B141" s="9">
         <v>46232.837026863424</v>
@@ -9744,7 +9750,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9771,13 +9777,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9787,7 +9793,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B142" s="5">
         <v>46232.83702931713</v>
@@ -9797,7 +9803,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9824,13 +9830,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9840,7 +9846,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B143" s="9">
         <v>46232.83703243056</v>
@@ -9850,7 +9856,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9877,13 +9883,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9893,7 +9899,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B144" s="5">
         <v>46232.83703607639</v>
@@ -9903,7 +9909,7 @@
         <v>46233.65522326389</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9930,13 +9936,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9946,7 +9952,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B145" s="9">
         <v>46232.837081481484</v>
@@ -9956,7 +9962,7 @@
         <v>46233.655218796295</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -9983,13 +9989,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9999,7 +10005,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B146" s="5">
         <v>46232.83713237269</v>
@@ -10009,7 +10015,7 @@
         <v>46233.65437712963</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10036,13 +10042,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q146" s="5">
         <v>46352</v>
@@ -10062,7 +10068,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B147" s="9">
         <v>46232.83714167824</v>
@@ -10099,13 +10105,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O147" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10115,7 +10121,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B148" s="5">
         <v>46232.83714405092</v>
@@ -10152,13 +10158,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10168,7 +10174,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B149" s="9">
         <v>46232.83714697917</v>
@@ -10205,13 +10211,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10221,7 +10227,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B150" s="5">
         <v>46232.837150555555</v>
@@ -10258,13 +10264,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10274,7 +10280,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B151" s="9">
         <v>46232.837152928245</v>
@@ -10311,13 +10317,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O151" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10327,7 +10333,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B152" s="5">
         <v>46232.83715663194</v>
@@ -10337,7 +10343,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10364,13 +10370,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10380,7 +10386,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B153" s="9">
         <v>46232.83715961805</v>
@@ -10390,7 +10396,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10417,13 +10423,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10433,7 +10439,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B154" s="5">
         <v>46232.83716207176</v>
@@ -10443,7 +10449,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10470,13 +10476,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10486,7 +10492,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B155" s="9">
         <v>46232.837165324076</v>
@@ -10496,7 +10502,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10523,13 +10529,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10539,7 +10545,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B156" s="5">
         <v>46232.83716826389</v>
@@ -10549,7 +10555,7 @@
         <v>46233.6553440162</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10576,13 +10582,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10592,7 +10598,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B157" s="9">
         <v>46232.837171782405</v>
@@ -10602,7 +10608,7 @@
         <v>46233.65534616898</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10629,13 +10635,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10645,7 +10651,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B158" s="5">
         <v>46232.837259120366</v>
@@ -10655,7 +10661,7 @@
         <v>46233.654372743054</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10682,10 +10688,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10708,7 +10714,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B159" s="9">
         <v>46232.83726530093</v>
@@ -10745,13 +10751,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10761,7 +10767,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B160" s="5">
         <v>46232.83726976852</v>
@@ -10798,13 +10804,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10814,7 +10820,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B161" s="9">
         <v>46232.83727541666</v>
@@ -10851,13 +10857,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10867,7 +10873,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B162" s="5">
         <v>46232.83727971065</v>
@@ -10904,13 +10910,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10920,7 +10926,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B163" s="9">
         <v>46232.83728435185</v>
@@ -10957,13 +10963,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10973,7 +10979,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B164" s="5">
         <v>46232.837293495366</v>
@@ -10983,7 +10989,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11010,13 +11016,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11026,7 +11032,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B165" s="9">
         <v>46232.83729747686</v>
@@ -11036,7 +11042,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11063,13 +11069,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11079,7 +11085,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B166" s="5">
         <v>46232.83730121527</v>
@@ -11089,7 +11095,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11116,13 +11122,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11132,7 +11138,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B167" s="9">
         <v>46232.83730554398</v>
@@ -11142,7 +11148,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11169,13 +11175,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11185,7 +11191,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B168" s="5">
         <v>46232.837309525465</v>
@@ -11195,7 +11201,7 @@
         <v>46233.65548366898</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11222,13 +11228,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11238,7 +11244,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B169" s="9">
         <v>46232.83731364583</v>
@@ -11248,7 +11254,7 @@
         <v>46233.65547903936</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11275,13 +11281,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11291,7 +11297,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B170" s="5">
         <v>46232.83737395833</v>
@@ -11301,7 +11307,7 @@
         <v>46233.65577939815</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11328,10 +11334,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11354,7 +11360,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B171" s="9">
         <v>46232.837430740736</v>
@@ -11391,13 +11397,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O171" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11407,7 +11413,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B172" s="5">
         <v>46232.83743509259</v>
@@ -11444,13 +11450,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11460,7 +11466,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B173" s="9">
         <v>46232.83743893518</v>
@@ -11497,13 +11503,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O173" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11513,7 +11519,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B174" s="5">
         <v>46232.837442442134</v>
@@ -11550,13 +11556,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11566,7 +11572,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B175" s="9">
         <v>46232.83744613426</v>
@@ -11603,13 +11609,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O175" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11619,7 +11625,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B176" s="5">
         <v>46232.83744990741</v>
@@ -11629,7 +11635,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11656,13 +11662,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11672,7 +11678,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B177" s="9">
         <v>46232.83745327547</v>
@@ -11682,7 +11688,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11709,13 +11715,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11725,7 +11731,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B178" s="5">
         <v>46232.837456712965</v>
@@ -11735,7 +11741,7 @@
         <v>46233.65578273148</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11762,13 +11768,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11778,7 +11784,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B179" s="9">
         <v>46232.83746033565</v>
@@ -11788,7 +11794,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11815,13 +11821,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11831,7 +11837,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B180" s="5">
         <v>46232.837463703705</v>
@@ -11841,7 +11847,7 @@
         <v>46233.65578369213</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11868,13 +11874,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11884,7 +11890,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B181" s="9">
         <v>46232.837467488425</v>
@@ -11894,7 +11900,7 @@
         <v>46233.65578417824</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -11921,13 +11927,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11937,7 +11943,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B182" s="5">
         <v>46232.837520092595</v>
@@ -11947,7 +11953,7 @@
         <v>46233.64911908565</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>25</v>
@@ -11971,7 +11977,7 @@
         <v>26</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>26</v>
@@ -11984,7 +11990,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B183" s="9">
         <v>46232.837524166665</v>
@@ -11994,16 +12000,16 @@
         <v>46233.65600935185</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I183" s="9">
         <v>46359</v>
@@ -12021,13 +12027,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q183" s="9">
         <v>46359</v>
@@ -12047,7 +12053,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B184" s="5">
         <v>46232.83753128472</v>
@@ -12063,10 +12069,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I184" s="5">
         <v>46359</v>
@@ -12084,13 +12090,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12100,7 +12106,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B185" s="9">
         <v>46232.837534942126</v>
@@ -12116,10 +12122,10 @@
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I185" s="9">
         <v>46359</v>
@@ -12137,13 +12143,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O185" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12153,7 +12159,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B186" s="5">
         <v>46232.83754447917</v>
@@ -12169,10 +12175,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I186" s="5">
         <v>46359</v>
@@ -12190,13 +12196,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12206,7 +12212,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B187" s="9">
         <v>46232.837548483796</v>
@@ -12222,10 +12228,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I187" s="9">
         <v>46359</v>
@@ -12243,13 +12249,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O187" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12259,7 +12265,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B188" s="5">
         <v>46232.837551793986</v>
@@ -12275,10 +12281,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I188" s="5">
         <v>46359</v>
@@ -12296,13 +12302,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12312,7 +12318,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B189" s="9">
         <v>46232.83755571759</v>
@@ -12322,16 +12328,16 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I189" s="9">
         <v>46359</v>
@@ -12349,13 +12355,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12365,7 +12371,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B190" s="5">
         <v>46232.837559548614</v>
@@ -12375,16 +12381,16 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I190" s="5">
         <v>46359</v>
@@ -12402,13 +12408,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12418,7 +12424,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B191" s="9">
         <v>46232.83756364584</v>
@@ -12428,16 +12434,16 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I191" s="9">
         <v>46359</v>
@@ -12455,13 +12461,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12471,7 +12477,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B192" s="5">
         <v>46232.83756778935</v>
@@ -12481,16 +12487,16 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I192" s="5">
         <v>46359</v>
@@ -12508,13 +12514,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12524,7 +12530,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B193" s="9">
         <v>46232.837571689815</v>
@@ -12534,16 +12540,16 @@
         <v>46233.65596739583</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I193" s="9">
         <v>46359</v>
@@ -12561,13 +12567,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12577,7 +12583,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B194" s="5">
         <v>46232.837575937505</v>
@@ -12587,16 +12593,16 @@
         <v>46233.65596230324</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I194" s="5">
         <v>46359</v>
@@ -12614,13 +12620,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12630,7 +12636,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B195" s="9">
         <v>46232.83768009259</v>
@@ -12640,7 +12646,7 @@
         <v>46233.65682853009</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12667,10 +12673,10 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P195" s="10" t="s">
         <v>26</v>
@@ -12693,7 +12699,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B196" s="5">
         <v>46232.83768599537</v>
@@ -12703,7 +12709,7 @@
         <v>46233.657000231484</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12730,13 +12736,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12746,7 +12752,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B197" s="9">
         <v>46232.83768928241</v>
@@ -12756,7 +12762,7 @@
         <v>46233.65699701389</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12783,13 +12789,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12799,7 +12805,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B198" s="5">
         <v>46232.837693043984</v>
@@ -12836,13 +12842,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12852,7 +12858,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B199" s="9">
         <v>46232.837696539355</v>
@@ -12889,13 +12895,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12905,7 +12911,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B200" s="5">
         <v>46232.837700069445</v>
@@ -12915,7 +12921,7 @@
         <v>46233.65698699074</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -12942,13 +12948,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12958,7 +12964,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B201" s="9">
         <v>46232.837703680554</v>
@@ -12968,7 +12974,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -12995,13 +13001,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13011,7 +13017,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B202" s="5">
         <v>46232.837707175924</v>
@@ -13021,7 +13027,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13048,13 +13054,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13064,7 +13070,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B203" s="9">
         <v>46232.837710555556</v>
@@ -13074,7 +13080,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13101,13 +13107,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13117,7 +13123,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B204" s="5">
         <v>46232.837713981484</v>
@@ -13127,7 +13133,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13154,13 +13160,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13170,7 +13176,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B205" s="9">
         <v>46232.83771748842</v>
@@ -13180,7 +13186,7 @@
         <v>46233.65697043981</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13207,13 +13213,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13223,7 +13229,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B206" s="5">
         <v>46232.83772105324</v>
@@ -13233,7 +13239,7 @@
         <v>46233.656965925926</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13260,13 +13266,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13276,7 +13282,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B207" s="9">
         <v>46232.837813125</v>
@@ -13286,16 +13292,16 @@
         <v>46233.65713384259</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I207" s="9">
         <v>46363</v>
@@ -13313,13 +13319,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q207" s="9">
         <v>46363</v>
@@ -13339,7 +13345,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B208" s="5">
         <v>46232.837821180554</v>
@@ -13355,10 +13361,10 @@
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I208" s="5">
         <v>46363</v>
@@ -13376,13 +13382,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13392,7 +13398,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B209" s="9">
         <v>46232.83782461805</v>
@@ -13408,10 +13414,10 @@
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I209" s="9">
         <v>46363</v>
@@ -13429,13 +13435,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13445,7 +13451,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B210" s="5">
         <v>46232.83782971065</v>
@@ -13461,10 +13467,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I210" s="5">
         <v>46363</v>
@@ -13482,13 +13488,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13498,7 +13504,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B211" s="9">
         <v>46232.83783466435</v>
@@ -13514,10 +13520,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I211" s="9">
         <v>46363</v>
@@ -13535,13 +13541,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13551,7 +13557,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B212" s="5">
         <v>46232.837839907406</v>
@@ -13567,10 +13573,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I212" s="5">
         <v>46363</v>
@@ -13588,13 +13594,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13604,7 +13610,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B213" s="9">
         <v>46232.83784550926</v>
@@ -13614,16 +13620,16 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I213" s="9">
         <v>46363</v>
@@ -13641,13 +13647,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13657,7 +13663,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B214" s="5">
         <v>46232.837850254626</v>
@@ -13667,16 +13673,16 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I214" s="5">
         <v>46363</v>
@@ -13694,13 +13700,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13710,7 +13716,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B215" s="9">
         <v>46232.83785502314</v>
@@ -13720,16 +13726,16 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I215" s="9">
         <v>46363</v>
@@ -13747,13 +13753,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13763,7 +13769,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B216" s="5">
         <v>46232.83785935185</v>
@@ -13773,16 +13779,16 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I216" s="5">
         <v>46363</v>
@@ -13800,13 +13806,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13816,7 +13822,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B217" s="9">
         <v>46232.83786371528</v>
@@ -13826,16 +13832,16 @@
         <v>46233.65709552083</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I217" s="9">
         <v>46363</v>
@@ -13853,13 +13859,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13869,7 +13875,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B218" s="5">
         <v>46232.83786809028</v>
@@ -13879,16 +13885,16 @@
         <v>46233.657091076384</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I218" s="5">
         <v>46363</v>
@@ -13906,13 +13912,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13922,7 +13928,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B219" s="9">
         <v>46232.837973483794</v>
@@ -13932,16 +13938,16 @@
         <v>46233.65731422453</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I219" s="9">
         <v>46364</v>
@@ -13959,13 +13965,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Q219" s="9">
         <v>46364</v>
@@ -13985,7 +13991,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B220" s="5">
         <v>46232.83798329861</v>
@@ -14001,10 +14007,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I220" s="5">
         <v>46364</v>
@@ -14022,13 +14028,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14038,7 +14044,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B221" s="9">
         <v>46232.83798822916</v>
@@ -14054,10 +14060,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I221" s="9">
         <v>46364</v>
@@ -14075,13 +14081,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O221" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14091,7 +14097,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B222" s="5">
         <v>46232.837992430555</v>
@@ -14107,10 +14113,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I222" s="5">
         <v>46364</v>
@@ -14128,13 +14134,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14144,7 +14150,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B223" s="9">
         <v>46232.83799675926</v>
@@ -14160,10 +14166,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I223" s="9">
         <v>46364</v>
@@ -14181,13 +14187,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O223" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14197,7 +14203,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B224" s="5">
         <v>46232.83800077546</v>
@@ -14213,10 +14219,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I224" s="5">
         <v>46364</v>
@@ -14234,13 +14240,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14250,7 +14256,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B225" s="9">
         <v>46232.838005439815</v>
@@ -14260,16 +14266,16 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I225" s="9">
         <v>46364</v>
@@ -14287,13 +14293,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14303,7 +14309,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B226" s="5">
         <v>46232.838009259256</v>
@@ -14313,16 +14319,16 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I226" s="5">
         <v>46364</v>
@@ -14340,13 +14346,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14356,7 +14362,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B227" s="9">
         <v>46232.83801302083</v>
@@ -14366,16 +14372,16 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I227" s="9">
         <v>46364</v>
@@ -14393,13 +14399,13 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14409,7 +14415,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B228" s="5">
         <v>46232.83801685185</v>
@@ -14419,16 +14425,16 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I228" s="5">
         <v>46364</v>
@@ -14446,13 +14452,13 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14462,7 +14468,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B229" s="9">
         <v>46232.838020497686</v>
@@ -14472,16 +14478,16 @@
         <v>46233.657285520836</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I229" s="9">
         <v>46364</v>
@@ -14499,13 +14505,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14515,7 +14521,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B230" s="5">
         <v>46232.83802429398</v>
@@ -14525,16 +14531,16 @@
         <v>46233.657280775464</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I230" s="5">
         <v>46364</v>
@@ -14552,13 +14558,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14568,7 +14574,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B231" s="9">
         <v>46232.83807947917</v>
@@ -14578,7 +14584,7 @@
         <v>46233.65049251157</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>25</v>
@@ -14602,7 +14608,7 @@
         <v>26</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>26</v>
@@ -14615,7 +14621,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B232" s="5">
         <v>46232.83808368056</v>
@@ -14625,16 +14631,16 @@
         <v>46233.65060152778</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I232" s="5">
         <v>46365</v>
@@ -14652,13 +14658,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q232" s="5">
         <v>46373</v>
@@ -14678,7 +14684,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B233" s="9">
         <v>46232.83812608796</v>
@@ -14688,16 +14694,16 @@
         <v>46233.650601898145</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I233" s="9">
         <v>46365</v>
@@ -14715,13 +14721,13 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q233" s="9">
         <v>46373</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="484">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -491,9 +491,6 @@
   </si>
   <si>
     <t>Ingenieria y diseño:,Plano Definitivos  ot 4385- 4386  ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217003865116839</t>
@@ -2504,7 +2501,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46245.56746402778</v>
+        <v>46246.577574317125</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
@@ -4165,7 +4162,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46245.568238368054</v>
+        <v>46246.57396976852</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -4209,8 +4206,8 @@
       <c r="R39" s="9">
         <v>46239</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>144</v>
+      <c r="S39" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -4221,7 +4218,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46232.835908622685</v>
@@ -4231,16 +4228,16 @@
         <v>46245.17038899305</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -4274,7 +4271,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591185186</v>
@@ -4284,16 +4281,16 @@
         <v>46245.1703903125</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I41" s="9">
         <v>46239</v>
@@ -4327,7 +4324,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83591513889</v>
@@ -4337,7 +4334,7 @@
         <v>46245.56770357639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4367,10 +4364,10 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="Q42" s="5">
         <v>46274</v>
@@ -4390,7 +4387,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592005787</v>
@@ -4400,16 +4397,16 @@
         <v>46233.65265884259</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I43" s="9">
         <v>46268</v>
@@ -4427,13 +4424,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>139</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83592324074</v>
@@ -4453,16 +4450,16 @@
         <v>46233.65265393518</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4480,13 +4477,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4496,7 +4493,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83592622685</v>
@@ -4512,10 +4509,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I45" s="9">
         <v>46275</v>
@@ -4536,10 +4533,10 @@
         <v>136</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="Q45" s="9">
         <v>46275</v>
@@ -4559,7 +4556,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83594578704</v>
@@ -4569,16 +4566,16 @@
         <v>46233.65294552084</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I46" s="5">
         <v>46275</v>
@@ -4599,7 +4596,7 @@
         <v>64</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>64</v>
@@ -4612,7 +4609,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83594902778</v>
@@ -4622,16 +4619,16 @@
         <v>46233.65294082176</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I47" s="9">
         <v>46275</v>
@@ -4652,7 +4649,7 @@
         <v>64</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>64</v>
@@ -4665,7 +4662,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83595255787</v>
@@ -4675,16 +4672,16 @@
         <v>46233.65334809027</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4705,7 +4702,7 @@
         <v>136</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>136</v>
@@ -4728,7 +4725,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B49" s="9">
         <v>46232.835965266204</v>
@@ -4738,16 +4735,16 @@
         <v>46240.824282256945</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4765,13 +4762,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4781,7 +4778,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83597435185</v>
@@ -4791,16 +4788,16 @@
         <v>46240.824278125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46356</v>
@@ -4818,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4834,7 +4831,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B51" s="9">
         <v>46232.835996435184</v>
@@ -4844,16 +4841,16 @@
         <v>46240.82427431713</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="9">
         <v>46356</v>
@@ -4871,13 +4868,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4887,7 +4884,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83599960648</v>
@@ -4897,16 +4894,16 @@
         <v>46240.824270625</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I52" s="5">
         <v>46356</v>
@@ -4924,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4940,7 +4937,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B53" s="9">
         <v>46232.8360029051</v>
@@ -4950,16 +4947,16 @@
         <v>46240.824266550924</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I53" s="9">
         <v>46356</v>
@@ -4977,13 +4974,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4993,7 +4990,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B54" s="5">
         <v>46232.83600618056</v>
@@ -5003,16 +5000,16 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I54" s="5">
         <v>46356</v>
@@ -5030,13 +5027,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5046,7 +5043,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83600939815</v>
@@ -5056,16 +5053,16 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I55" s="9">
         <v>46356</v>
@@ -5083,13 +5080,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5099,7 +5096,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83601267361</v>
@@ -5109,16 +5106,16 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I56" s="5">
         <v>46356</v>
@@ -5136,13 +5133,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5152,7 +5149,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83601601852</v>
@@ -5162,16 +5159,16 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I57" s="9">
         <v>46356</v>
@@ -5189,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5205,7 +5202,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83601914352</v>
@@ -5215,16 +5212,16 @@
         <v>46240.824248414356</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I58" s="5">
         <v>46356</v>
@@ -5242,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5258,7 +5255,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83602246528</v>
@@ -5268,16 +5265,16 @@
         <v>46240.82424457176</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I59" s="9">
         <v>46356</v>
@@ -5295,13 +5292,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5311,7 +5308,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83611833333</v>
@@ -5321,7 +5318,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5345,7 +5342,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5358,7 +5355,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B61" s="9">
         <v>46232.836122465276</v>
@@ -5368,16 +5365,16 @@
         <v>46233.65395961805</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I61" s="9">
         <v>46293</v>
@@ -5395,13 +5392,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q61" s="9">
         <v>46294</v>
@@ -5421,7 +5418,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83612731482</v>
@@ -5431,16 +5428,16 @@
         <v>46233.65395623843</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46293</v>
@@ -5458,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q62" s="5">
         <v>46294</v>
@@ -5484,7 +5481,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83613222222</v>
@@ -5494,16 +5491,16 @@
         <v>46233.65395206018</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I63" s="9">
         <v>46293</v>
@@ -5521,13 +5518,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>105</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q63" s="9">
         <v>46294</v>
@@ -5547,7 +5544,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836136909726</v>
@@ -5557,7 +5554,7 @@
         <v>46233.65409758102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5584,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q64" s="5">
         <v>46295</v>
@@ -5610,7 +5607,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83614177084</v>
@@ -5620,7 +5617,7 @@
         <v>46233.65408881944</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5647,13 +5644,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q65" s="9">
         <v>46295</v>
@@ -5673,7 +5670,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B66" s="5">
         <v>46232.83614663195</v>
@@ -5683,7 +5680,7 @@
         <v>46233.65408491898</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5710,13 +5707,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q66" s="5">
         <v>46295</v>
@@ -5736,7 +5733,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B67" s="9">
         <v>46232.83615094908</v>
@@ -5746,7 +5743,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5770,7 +5767,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5783,7 +5780,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83615418982</v>
@@ -5799,10 +5796,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46296</v>
@@ -5820,13 +5817,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q68" s="5">
         <v>46304</v>
@@ -5846,7 +5843,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B69" s="9">
         <v>46232.83616251158</v>
@@ -5856,16 +5853,16 @@
         <v>46233.643562094905</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I69" s="9">
         <v>46307</v>
@@ -5883,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q69" s="9">
         <v>46324</v>
@@ -5909,7 +5906,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83616856481</v>
@@ -5919,16 +5916,16 @@
         <v>46233.64355409722</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I70" s="5">
         <v>46307</v>
@@ -5946,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5962,7 +5959,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B71" s="9">
         <v>46232.83617490741</v>
@@ -5972,16 +5969,16 @@
         <v>46233.64356298611</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I71" s="9">
         <v>46307</v>
@@ -5999,13 +5996,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O71" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>216</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6015,7 +6012,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B72" s="5">
         <v>46232.836181412036</v>
@@ -6025,16 +6022,16 @@
         <v>46233.643563680555</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I72" s="5">
         <v>46307</v>
@@ -6052,13 +6049,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6068,7 +6065,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B73" s="9">
         <v>46232.836188587964</v>
@@ -6078,16 +6075,16 @@
         <v>46233.643564259255</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I73" s="9">
         <v>46307</v>
@@ -6105,13 +6102,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6121,7 +6118,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B74" s="5">
         <v>46232.836193449075</v>
@@ -6131,16 +6128,16 @@
         <v>46233.64356484954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I74" s="5">
         <v>46307</v>
@@ -6158,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6174,7 +6171,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B75" s="9">
         <v>46232.83619825232</v>
@@ -6184,16 +6181,16 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I75" s="9">
         <v>46307</v>
@@ -6211,13 +6208,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6227,7 +6224,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B76" s="5">
         <v>46232.8362028125</v>
@@ -6237,16 +6234,16 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46307</v>
@@ -6264,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6280,7 +6277,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B77" s="9">
         <v>46232.83620730324</v>
@@ -6290,16 +6287,16 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I77" s="9">
         <v>46307</v>
@@ -6317,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6333,7 +6330,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B78" s="5">
         <v>46232.83621217593</v>
@@ -6343,16 +6340,16 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I78" s="5">
         <v>46307</v>
@@ -6370,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6386,7 +6383,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B79" s="9">
         <v>46232.8362174537</v>
@@ -6396,16 +6393,16 @@
         <v>46233.64356818287</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I79" s="9">
         <v>46307</v>
@@ -6423,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6439,7 +6436,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B80" s="5">
         <v>46232.836222025464</v>
@@ -6449,16 +6446,16 @@
         <v>46233.64356881945</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I80" s="5">
         <v>46307</v>
@@ -6476,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6492,7 +6489,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B81" s="9">
         <v>46232.836342152776</v>
@@ -6502,7 +6499,7 @@
         <v>46233.64375841436</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6529,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q81" s="9">
         <v>46328</v>
@@ -6555,7 +6552,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B82" s="5">
         <v>46232.83634841435</v>
@@ -6565,7 +6562,7 @@
         <v>46233.64386252315</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6592,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6608,7 +6605,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B83" s="9">
         <v>46232.836353125</v>
@@ -6618,7 +6615,7 @@
         <v>46233.643861793986</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6645,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6661,7 +6658,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B84" s="5">
         <v>46232.836358113425</v>
@@ -6671,7 +6668,7 @@
         <v>46233.643860972225</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6698,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6714,7 +6711,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B85" s="9">
         <v>46232.83636347222</v>
@@ -6724,7 +6721,7 @@
         <v>46233.643860219905</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6751,13 +6748,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6767,7 +6764,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B86" s="5">
         <v>46232.8363674537</v>
@@ -6777,7 +6774,7 @@
         <v>46233.64385969908</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6804,13 +6801,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6820,7 +6817,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B87" s="9">
         <v>46232.83637209491</v>
@@ -6830,7 +6827,7 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6857,13 +6854,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="P87" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="P87" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6873,7 +6870,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B88" s="5">
         <v>46232.836376666666</v>
@@ -6883,7 +6880,7 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6910,13 +6907,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6926,7 +6923,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B89" s="9">
         <v>46232.836381319445</v>
@@ -6936,7 +6933,7 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6963,13 +6960,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6979,7 +6976,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B90" s="5">
         <v>46232.83638501157</v>
@@ -6989,7 +6986,7 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7016,13 +7013,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7032,7 +7029,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B91" s="9">
         <v>46232.83638946759</v>
@@ -7042,7 +7039,7 @@
         <v>46233.64385625</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7069,13 +7066,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7085,7 +7082,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B92" s="5">
         <v>46232.836394108796</v>
@@ -7095,7 +7092,7 @@
         <v>46233.64382548611</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7122,13 +7119,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O92" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7138,7 +7135,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B93" s="9">
         <v>46232.836502499995</v>
@@ -7148,7 +7145,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -7172,7 +7169,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -7185,7 +7182,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B94" s="5">
         <v>46232.83650636574</v>
@@ -7195,16 +7192,16 @@
         <v>46241.191987488426</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I94" s="5">
         <v>46239</v>
@@ -7222,13 +7219,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q94" s="5">
         <v>46240</v>
@@ -7248,7 +7245,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B95" s="9">
         <v>46232.836519247685</v>
@@ -7258,16 +7255,16 @@
         <v>46241.191987488426</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I95" s="9">
         <v>46239</v>
@@ -7285,13 +7282,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q95" s="9">
         <v>46240</v>
@@ -7311,7 +7308,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B96" s="5">
         <v>46232.83652788194</v>
@@ -7321,16 +7318,16 @@
         <v>46233.65424876157</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I96" s="5">
         <v>46343</v>
@@ -7348,13 +7345,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>131</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q96" s="5">
         <v>46344</v>
@@ -7374,7 +7371,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B97" s="9">
         <v>46232.83654054398</v>
@@ -7384,7 +7381,7 @@
         <v>46233.645743333334</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>25</v>
@@ -7408,7 +7405,7 @@
         <v>26</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>26</v>
@@ -7421,7 +7418,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B98" s="5">
         <v>46232.83654375</v>
@@ -7431,7 +7428,7 @@
         <v>46233.65439393518</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7458,13 +7455,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q98" s="5">
         <v>46346</v>
@@ -7484,7 +7481,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B99" s="9">
         <v>46232.83655042824</v>
@@ -7494,7 +7491,7 @@
         <v>46233.65452458333</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7521,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7537,7 +7534,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B100" s="5">
         <v>46232.836554814814</v>
@@ -7547,7 +7544,7 @@
         <v>46233.654521550925</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7574,13 +7571,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7590,7 +7587,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B101" s="9">
         <v>46232.836558854164</v>
@@ -7600,7 +7597,7 @@
         <v>46233.654517939816</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7627,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7643,7 +7640,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B102" s="5">
         <v>46232.83656295139</v>
@@ -7653,7 +7650,7 @@
         <v>46233.65451447917</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7680,13 +7677,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7696,7 +7693,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B103" s="9">
         <v>46232.83656672454</v>
@@ -7706,7 +7703,7 @@
         <v>46233.65451069444</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7733,13 +7730,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7749,7 +7746,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B104" s="5">
         <v>46232.836570162035</v>
@@ -7759,7 +7756,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7786,13 +7783,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7802,7 +7799,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46232.83657339121</v>
@@ -7812,7 +7809,7 @@
         <v>46233.65449810185</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7839,13 +7836,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7855,7 +7852,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B106" s="5">
         <v>46232.83657665509</v>
@@ -7865,7 +7862,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7892,13 +7889,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7908,7 +7905,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B107" s="9">
         <v>46232.83658011574</v>
@@ -7918,7 +7915,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7945,13 +7942,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7961,7 +7958,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B108" s="5">
         <v>46232.83658361111</v>
@@ -7971,7 +7968,7 @@
         <v>46233.654487141204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7998,13 +7995,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8014,7 +8011,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B109" s="9">
         <v>46232.83658716435</v>
@@ -8024,7 +8021,7 @@
         <v>46233.65448212963</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8051,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8067,7 +8064,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B110" s="5">
         <v>46232.83664298611</v>
@@ -8077,7 +8074,7 @@
         <v>46233.65438969908</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8104,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q110" s="5">
         <v>46349</v>
@@ -8130,7 +8127,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B111" s="9">
         <v>46232.836698935185</v>
@@ -8140,7 +8137,7 @@
         <v>46233.65466868055</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8167,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O111" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8183,7 +8180,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B112" s="5">
         <v>46232.83670696759</v>
@@ -8193,7 +8190,7 @@
         <v>46233.65466519676</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8220,13 +8217,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O112" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8236,7 +8233,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B113" s="9">
         <v>46232.836713020835</v>
@@ -8246,7 +8243,7 @@
         <v>46233.654662037035</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8273,13 +8270,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8289,7 +8286,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B114" s="5">
         <v>46232.83671971065</v>
@@ -8299,7 +8296,7 @@
         <v>46233.65465921296</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8326,13 +8323,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8342,7 +8339,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B115" s="9">
         <v>46232.83672694444</v>
@@ -8352,7 +8349,7 @@
         <v>46233.65465619213</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8379,13 +8376,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8395,7 +8392,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B116" s="5">
         <v>46232.8367334375</v>
@@ -8405,7 +8402,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8432,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8448,7 +8445,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B117" s="9">
         <v>46232.83673865741</v>
@@ -8458,7 +8455,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8485,13 +8482,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8501,7 +8498,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B118" s="5">
         <v>46232.83674337963</v>
@@ -8511,7 +8508,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8538,13 +8535,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8554,7 +8551,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B119" s="9">
         <v>46232.83674840278</v>
@@ -8564,7 +8561,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8591,13 +8588,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8607,7 +8604,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B120" s="5">
         <v>46232.83675357639</v>
@@ -8617,7 +8614,7 @@
         <v>46233.65463991898</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8644,13 +8641,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B121" s="9">
         <v>46232.83675886574</v>
@@ -8670,7 +8667,7 @@
         <v>46233.65463564815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8697,13 +8694,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8713,7 +8710,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B122" s="5">
         <v>46232.836891377316</v>
@@ -8723,7 +8720,7 @@
         <v>46233.65438556713</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8750,13 +8747,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q122" s="5">
         <v>46350</v>
@@ -8776,7 +8773,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B123" s="9">
         <v>46232.83690123842</v>
@@ -8786,7 +8783,7 @@
         <v>46233.654805949074</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8813,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8829,7 +8826,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B124" s="5">
         <v>46232.83690674769</v>
@@ -8839,7 +8836,7 @@
         <v>46233.654802523146</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8866,13 +8863,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8882,7 +8879,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B125" s="9">
         <v>46232.836911527775</v>
@@ -8892,7 +8889,7 @@
         <v>46233.65479875</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8919,13 +8916,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8935,7 +8932,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B126" s="5">
         <v>46232.836916238426</v>
@@ -8945,7 +8942,7 @@
         <v>46233.65479480324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8972,13 +8969,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8988,7 +8985,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B127" s="9">
         <v>46232.83692087963</v>
@@ -8998,7 +8995,7 @@
         <v>46233.65479153935</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9025,13 +9022,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9041,7 +9038,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B128" s="5">
         <v>46232.836924375</v>
@@ -9051,7 +9048,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9078,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9094,7 +9091,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B129" s="9">
         <v>46232.836927488424</v>
@@ -9104,7 +9101,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9131,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9147,7 +9144,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B130" s="5">
         <v>46232.836930474536</v>
@@ -9157,7 +9154,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9184,13 +9181,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9200,7 +9197,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B131" s="9">
         <v>46232.836933530096</v>
@@ -9210,7 +9207,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9237,13 +9234,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9253,7 +9250,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B132" s="5">
         <v>46232.83693686343</v>
@@ -9263,7 +9260,7 @@
         <v>46233.65477483797</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9290,13 +9287,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9306,7 +9303,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B133" s="9">
         <v>46232.83694028935</v>
@@ -9316,7 +9313,7 @@
         <v>46233.65477001158</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9343,13 +9340,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9359,7 +9356,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B134" s="5">
         <v>46232.836990428244</v>
@@ -9369,7 +9366,7 @@
         <v>46233.65438166667</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9396,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q134" s="5">
         <v>46351</v>
@@ -9422,7 +9419,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B135" s="9">
         <v>46232.837003043984</v>
@@ -9432,7 +9429,7 @@
         <v>46233.655253888894</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9459,13 +9456,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9475,7 +9472,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46232.837007395836</v>
@@ -9485,7 +9482,7 @@
         <v>46233.65525037037</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9512,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9528,7 +9525,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46232.83701138889</v>
@@ -9538,7 +9535,7 @@
         <v>46233.655246504626</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9565,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9581,7 +9578,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B138" s="5">
         <v>46232.83701560185</v>
@@ -9591,7 +9588,7 @@
         <v>46233.655243506946</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9618,13 +9615,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9634,7 +9631,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B139" s="9">
         <v>46232.83701969907</v>
@@ -9644,7 +9641,7 @@
         <v>46233.655239942134</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9671,13 +9668,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9687,7 +9684,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B140" s="5">
         <v>46232.83702368056</v>
@@ -9697,7 +9694,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9724,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9740,7 +9737,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B141" s="9">
         <v>46232.837026863424</v>
@@ -9750,7 +9747,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9777,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9793,7 +9790,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B142" s="5">
         <v>46232.83702931713</v>
@@ -9803,7 +9800,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9830,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9846,7 +9843,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B143" s="9">
         <v>46232.83703243056</v>
@@ -9856,7 +9853,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9883,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9899,7 +9896,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B144" s="5">
         <v>46232.83703607639</v>
@@ -9909,7 +9906,7 @@
         <v>46233.65522326389</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9936,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9952,7 +9949,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B145" s="9">
         <v>46232.837081481484</v>
@@ -9962,7 +9959,7 @@
         <v>46233.655218796295</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -9989,13 +9986,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10005,7 +10002,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B146" s="5">
         <v>46232.83713237269</v>
@@ -10015,7 +10012,7 @@
         <v>46233.65437712963</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10042,13 +10039,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O146" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="P146" s="6" t="s">
         <v>352</v>
-      </c>
-      <c r="P146" s="6" t="s">
-        <v>353</v>
       </c>
       <c r="Q146" s="5">
         <v>46352</v>
@@ -10068,7 +10065,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B147" s="9">
         <v>46232.83714167824</v>
@@ -10078,7 +10075,7 @@
         <v>46233.655379131946</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10105,13 +10102,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10121,7 +10118,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B148" s="5">
         <v>46232.83714405092</v>
@@ -10131,7 +10128,7 @@
         <v>46233.65537608796</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10158,13 +10155,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10174,7 +10171,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B149" s="9">
         <v>46232.83714697917</v>
@@ -10184,7 +10181,7 @@
         <v>46233.65537255787</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10211,13 +10208,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10227,7 +10224,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B150" s="5">
         <v>46232.837150555555</v>
@@ -10237,7 +10234,7 @@
         <v>46233.65536958333</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10264,13 +10261,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10280,7 +10277,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B151" s="9">
         <v>46232.837152928245</v>
@@ -10290,7 +10287,7 @@
         <v>46233.655366527775</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10317,13 +10314,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10333,7 +10330,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B152" s="5">
         <v>46232.83715663194</v>
@@ -10343,7 +10340,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10370,13 +10367,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10386,7 +10383,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B153" s="9">
         <v>46232.83715961805</v>
@@ -10396,7 +10393,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10423,13 +10420,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10439,7 +10436,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B154" s="5">
         <v>46232.83716207176</v>
@@ -10449,7 +10446,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10476,13 +10473,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10492,7 +10489,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B155" s="9">
         <v>46232.837165324076</v>
@@ -10502,7 +10499,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10529,13 +10526,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10545,7 +10542,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B156" s="5">
         <v>46232.83716826389</v>
@@ -10555,7 +10552,7 @@
         <v>46233.6553440162</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10582,13 +10579,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10598,7 +10595,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B157" s="9">
         <v>46232.837171782405</v>
@@ -10608,7 +10605,7 @@
         <v>46233.65534616898</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10635,13 +10632,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10651,7 +10648,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B158" s="5">
         <v>46232.837259120366</v>
@@ -10661,7 +10658,7 @@
         <v>46233.654372743054</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10688,10 +10685,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10714,7 +10711,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B159" s="9">
         <v>46232.83726530093</v>
@@ -10724,7 +10721,7 @@
         <v>46233.65551298611</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10751,13 +10748,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10767,7 +10764,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B160" s="5">
         <v>46232.83726976852</v>
@@ -10777,7 +10774,7 @@
         <v>46233.65550966436</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10804,13 +10801,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10820,7 +10817,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B161" s="9">
         <v>46232.83727541666</v>
@@ -10830,7 +10827,7 @@
         <v>46233.65550638889</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10857,13 +10854,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10873,7 +10870,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B162" s="5">
         <v>46232.83727971065</v>
@@ -10883,7 +10880,7 @@
         <v>46233.655503194444</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10910,13 +10907,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10926,7 +10923,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B163" s="9">
         <v>46232.83728435185</v>
@@ -10936,7 +10933,7 @@
         <v>46233.65549978009</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -10963,13 +10960,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10979,7 +10976,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B164" s="5">
         <v>46232.837293495366</v>
@@ -10989,7 +10986,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11016,13 +11013,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11032,7 +11029,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B165" s="9">
         <v>46232.83729747686</v>
@@ -11042,7 +11039,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11069,13 +11066,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11085,7 +11082,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B166" s="5">
         <v>46232.83730121527</v>
@@ -11095,7 +11092,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11122,13 +11119,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11138,7 +11135,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B167" s="9">
         <v>46232.83730554398</v>
@@ -11148,7 +11145,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11175,13 +11172,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11191,7 +11188,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B168" s="5">
         <v>46232.837309525465</v>
@@ -11201,7 +11198,7 @@
         <v>46233.65548366898</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11228,13 +11225,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11244,7 +11241,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B169" s="9">
         <v>46232.83731364583</v>
@@ -11254,7 +11251,7 @@
         <v>46233.65547903936</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11281,13 +11278,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11297,7 +11294,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B170" s="5">
         <v>46232.83737395833</v>
@@ -11307,7 +11304,7 @@
         <v>46233.65577939815</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11334,10 +11331,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11360,7 +11357,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B171" s="9">
         <v>46232.837430740736</v>
@@ -11370,7 +11367,7 @@
         <v>46233.655769930556</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11397,13 +11394,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11413,7 +11410,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B172" s="5">
         <v>46232.83743509259</v>
@@ -11423,7 +11420,7 @@
         <v>46233.6557796875</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11450,13 +11447,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11466,7 +11463,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B173" s="9">
         <v>46232.83743893518</v>
@@ -11476,7 +11473,7 @@
         <v>46233.65578027778</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11503,13 +11500,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11519,7 +11516,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B174" s="5">
         <v>46232.837442442134</v>
@@ -11529,7 +11526,7 @@
         <v>46233.65578074074</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11556,13 +11553,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11572,7 +11569,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B175" s="9">
         <v>46232.83744613426</v>
@@ -11582,7 +11579,7 @@
         <v>46233.65578128472</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11609,13 +11606,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11625,7 +11622,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B176" s="5">
         <v>46232.83744990741</v>
@@ -11635,7 +11632,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11662,13 +11659,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11678,7 +11675,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B177" s="9">
         <v>46232.83745327547</v>
@@ -11688,7 +11685,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11715,13 +11712,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11731,7 +11728,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B178" s="5">
         <v>46232.837456712965</v>
@@ -11741,7 +11738,7 @@
         <v>46233.65578273148</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11768,13 +11765,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11784,7 +11781,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B179" s="9">
         <v>46232.83746033565</v>
@@ -11794,7 +11791,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11821,13 +11818,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11837,7 +11834,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B180" s="5">
         <v>46232.837463703705</v>
@@ -11847,7 +11844,7 @@
         <v>46233.65578369213</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11874,13 +11871,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11890,7 +11887,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B181" s="9">
         <v>46232.837467488425</v>
@@ -11900,7 +11897,7 @@
         <v>46233.65578417824</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -11927,13 +11924,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11943,7 +11940,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B182" s="5">
         <v>46232.837520092595</v>
@@ -11953,7 +11950,7 @@
         <v>46233.64911908565</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>25</v>
@@ -11977,7 +11974,7 @@
         <v>26</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>26</v>
@@ -11990,7 +11987,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B183" s="9">
         <v>46232.837524166665</v>
@@ -12000,16 +11997,16 @@
         <v>46233.65600935185</v>
       </c>
       <c r="E183" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F183" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G183" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="F183" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G183" s="10" t="s">
+      <c r="H183" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I183" s="9">
         <v>46359</v>
@@ -12027,13 +12024,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O183" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="P183" s="10" t="s">
         <v>405</v>
-      </c>
-      <c r="P183" s="10" t="s">
-        <v>406</v>
       </c>
       <c r="Q183" s="9">
         <v>46359</v>
@@ -12053,7 +12050,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B184" s="5">
         <v>46232.83753128472</v>
@@ -12063,16 +12060,16 @@
         <v>46233.65599796297</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I184" s="5">
         <v>46359</v>
@@ -12090,13 +12087,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12106,7 +12103,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B185" s="9">
         <v>46232.837534942126</v>
@@ -12116,16 +12113,16 @@
         <v>46233.65599480324</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H185" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H185" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I185" s="9">
         <v>46359</v>
@@ -12143,13 +12140,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12159,7 +12156,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B186" s="5">
         <v>46232.83754447917</v>
@@ -12169,16 +12166,16 @@
         <v>46233.655991527776</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I186" s="5">
         <v>46359</v>
@@ -12196,13 +12193,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12212,7 +12209,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B187" s="9">
         <v>46232.837548483796</v>
@@ -12222,16 +12219,16 @@
         <v>46233.65598818287</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H187" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H187" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I187" s="9">
         <v>46359</v>
@@ -12249,13 +12246,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12265,7 +12262,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B188" s="5">
         <v>46232.837551793986</v>
@@ -12275,16 +12272,16 @@
         <v>46233.65598459491</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I188" s="5">
         <v>46359</v>
@@ -12302,13 +12299,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12318,7 +12315,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B189" s="9">
         <v>46232.83755571759</v>
@@ -12328,16 +12325,16 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H189" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H189" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I189" s="9">
         <v>46359</v>
@@ -12355,13 +12352,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12371,7 +12368,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B190" s="5">
         <v>46232.837559548614</v>
@@ -12381,16 +12378,16 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I190" s="5">
         <v>46359</v>
@@ -12408,13 +12405,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12424,7 +12421,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B191" s="9">
         <v>46232.83756364584</v>
@@ -12434,16 +12431,16 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H191" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H191" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I191" s="9">
         <v>46359</v>
@@ -12461,13 +12458,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12477,7 +12474,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B192" s="5">
         <v>46232.83756778935</v>
@@ -12487,16 +12484,16 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I192" s="5">
         <v>46359</v>
@@ -12514,13 +12511,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12530,7 +12527,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B193" s="9">
         <v>46232.837571689815</v>
@@ -12540,16 +12537,16 @@
         <v>46233.65596739583</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H193" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="H193" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="I193" s="9">
         <v>46359</v>
@@ -12567,13 +12564,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12583,7 +12580,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B194" s="5">
         <v>46232.837575937505</v>
@@ -12593,16 +12590,16 @@
         <v>46233.65596230324</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="I194" s="5">
         <v>46359</v>
@@ -12620,13 +12617,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12636,7 +12633,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B195" s="9">
         <v>46232.83768009259</v>
@@ -12646,7 +12643,7 @@
         <v>46233.65682853009</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12673,10 +12670,10 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P195" s="10" t="s">
         <v>26</v>
@@ -12699,7 +12696,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B196" s="5">
         <v>46232.83768599537</v>
@@ -12709,7 +12706,7 @@
         <v>46233.657000231484</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12736,13 +12733,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12752,7 +12749,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B197" s="9">
         <v>46232.83768928241</v>
@@ -12762,7 +12759,7 @@
         <v>46233.65699701389</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12789,13 +12786,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12805,7 +12802,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B198" s="5">
         <v>46232.837693043984</v>
@@ -12815,7 +12812,7 @@
         <v>46233.6569934375</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12842,13 +12839,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12858,7 +12855,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B199" s="9">
         <v>46232.837696539355</v>
@@ -12868,7 +12865,7 @@
         <v>46233.65699033564</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -12895,13 +12892,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12911,7 +12908,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B200" s="5">
         <v>46232.837700069445</v>
@@ -12921,7 +12918,7 @@
         <v>46233.65698699074</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -12948,13 +12945,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12964,7 +12961,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B201" s="9">
         <v>46232.837703680554</v>
@@ -12974,7 +12971,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13001,13 +12998,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13017,7 +13014,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B202" s="5">
         <v>46232.837707175924</v>
@@ -13027,7 +13024,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13054,13 +13051,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13070,7 +13067,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B203" s="9">
         <v>46232.837710555556</v>
@@ -13080,7 +13077,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13107,13 +13104,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13123,7 +13120,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B204" s="5">
         <v>46232.837713981484</v>
@@ -13133,7 +13130,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13160,13 +13157,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13176,7 +13173,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B205" s="9">
         <v>46232.83771748842</v>
@@ -13186,7 +13183,7 @@
         <v>46233.65697043981</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13213,13 +13210,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13229,7 +13226,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B206" s="5">
         <v>46232.83772105324</v>
@@ -13239,7 +13236,7 @@
         <v>46233.656965925926</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13266,13 +13263,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13282,7 +13279,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B207" s="9">
         <v>46232.837813125</v>
@@ -13292,16 +13289,16 @@
         <v>46233.65713384259</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I207" s="9">
         <v>46363</v>
@@ -13319,13 +13316,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q207" s="9">
         <v>46363</v>
@@ -13345,7 +13342,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B208" s="5">
         <v>46232.837821180554</v>
@@ -13355,16 +13352,16 @@
         <v>46233.65712715278</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I208" s="5">
         <v>46363</v>
@@ -13382,13 +13379,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13398,7 +13395,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B209" s="9">
         <v>46232.83782461805</v>
@@ -13408,16 +13405,16 @@
         <v>46233.657123854166</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I209" s="9">
         <v>46363</v>
@@ -13435,13 +13432,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13451,7 +13448,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B210" s="5">
         <v>46232.83782971065</v>
@@ -13461,16 +13458,16 @@
         <v>46233.6571202662</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I210" s="5">
         <v>46363</v>
@@ -13488,13 +13485,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13504,7 +13501,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B211" s="9">
         <v>46232.83783466435</v>
@@ -13514,16 +13511,16 @@
         <v>46233.65711684027</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I211" s="9">
         <v>46363</v>
@@ -13541,13 +13538,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13557,7 +13554,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B212" s="5">
         <v>46232.837839907406</v>
@@ -13567,16 +13564,16 @@
         <v>46233.65711247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I212" s="5">
         <v>46363</v>
@@ -13594,13 +13591,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13610,7 +13607,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B213" s="9">
         <v>46232.83784550926</v>
@@ -13620,16 +13617,16 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I213" s="9">
         <v>46363</v>
@@ -13647,13 +13644,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13663,7 +13660,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B214" s="5">
         <v>46232.837850254626</v>
@@ -13673,16 +13670,16 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I214" s="5">
         <v>46363</v>
@@ -13700,13 +13697,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13716,7 +13713,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B215" s="9">
         <v>46232.83785502314</v>
@@ -13726,16 +13723,16 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I215" s="9">
         <v>46363</v>
@@ -13753,13 +13750,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13769,7 +13766,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B216" s="5">
         <v>46232.83785935185</v>
@@ -13779,16 +13776,16 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I216" s="5">
         <v>46363</v>
@@ -13806,13 +13803,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13822,7 +13819,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B217" s="9">
         <v>46232.83786371528</v>
@@ -13832,16 +13829,16 @@
         <v>46233.65709552083</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I217" s="9">
         <v>46363</v>
@@ -13859,13 +13856,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13875,7 +13872,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B218" s="5">
         <v>46232.83786809028</v>
@@ -13885,16 +13882,16 @@
         <v>46233.657091076384</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I218" s="5">
         <v>46363</v>
@@ -13912,13 +13909,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13928,7 +13925,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B219" s="9">
         <v>46232.837973483794</v>
@@ -13938,16 +13935,16 @@
         <v>46233.65731422453</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I219" s="9">
         <v>46364</v>
@@ -13965,13 +13962,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O219" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="P219" s="10" t="s">
         <v>460</v>
-      </c>
-      <c r="P219" s="10" t="s">
-        <v>461</v>
       </c>
       <c r="Q219" s="9">
         <v>46364</v>
@@ -13991,7 +13988,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B220" s="5">
         <v>46232.83798329861</v>
@@ -14001,16 +13998,16 @@
         <v>46233.65731456019</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I220" s="5">
         <v>46364</v>
@@ -14028,13 +14025,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14044,7 +14041,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B221" s="9">
         <v>46232.83798822916</v>
@@ -14054,16 +14051,16 @@
         <v>46233.65731164352</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I221" s="9">
         <v>46364</v>
@@ -14081,13 +14078,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14097,7 +14094,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B222" s="5">
         <v>46232.837992430555</v>
@@ -14107,16 +14104,16 @@
         <v>46233.6573087963</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I222" s="5">
         <v>46364</v>
@@ -14134,13 +14131,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14150,7 +14147,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B223" s="9">
         <v>46232.83799675926</v>
@@ -14160,16 +14157,16 @@
         <v>46233.657305381945</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I223" s="9">
         <v>46364</v>
@@ -14187,13 +14184,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14203,7 +14200,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B224" s="5">
         <v>46232.83800077546</v>
@@ -14213,16 +14210,16 @@
         <v>46233.65730237268</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I224" s="5">
         <v>46364</v>
@@ -14240,13 +14237,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14256,7 +14253,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B225" s="9">
         <v>46232.838005439815</v>
@@ -14266,16 +14263,16 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I225" s="9">
         <v>46364</v>
@@ -14293,13 +14290,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14309,7 +14306,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B226" s="5">
         <v>46232.838009259256</v>
@@ -14319,16 +14316,16 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I226" s="5">
         <v>46364</v>
@@ -14346,13 +14343,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14362,7 +14359,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B227" s="9">
         <v>46232.83801302083</v>
@@ -14372,16 +14369,16 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I227" s="9">
         <v>46364</v>
@@ -14399,13 +14396,13 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14415,7 +14412,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B228" s="5">
         <v>46232.83801685185</v>
@@ -14425,16 +14422,16 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I228" s="5">
         <v>46364</v>
@@ -14452,13 +14449,13 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14468,7 +14465,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B229" s="9">
         <v>46232.838020497686</v>
@@ -14478,16 +14475,16 @@
         <v>46233.657285520836</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I229" s="9">
         <v>46364</v>
@@ -14505,13 +14502,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14521,7 +14518,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B230" s="5">
         <v>46232.83802429398</v>
@@ -14531,16 +14528,16 @@
         <v>46233.657280775464</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I230" s="5">
         <v>46364</v>
@@ -14558,13 +14555,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14574,7 +14571,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B231" s="9">
         <v>46232.83807947917</v>
@@ -14584,7 +14581,7 @@
         <v>46233.65049251157</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>25</v>
@@ -14608,7 +14605,7 @@
         <v>26</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>26</v>
@@ -14621,7 +14618,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B232" s="5">
         <v>46232.83808368056</v>
@@ -14631,16 +14628,16 @@
         <v>46233.65060152778</v>
       </c>
       <c r="E232" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G232" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="F232" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G232" s="6" t="s">
+      <c r="H232" s="6" t="s">
         <v>479</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>480</v>
       </c>
       <c r="I232" s="5">
         <v>46365</v>
@@ -14658,13 +14655,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q232" s="5">
         <v>46373</v>
@@ -14684,7 +14681,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B233" s="9">
         <v>46232.83812608796</v>
@@ -14694,16 +14691,16 @@
         <v>46233.650601898145</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>479</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>480</v>
       </c>
       <c r="I233" s="9">
         <v>46365</v>
@@ -14721,13 +14718,13 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q233" s="9">
         <v>46373</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -432,7 +432,7 @@
     <t>Generacion Oc ot 4385- 4386</t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t>Fabricación externa   ot 4386 ,Armado  OT ot 4385- 4386</t>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46237.55371795139</v>
+        <v>46254.647308750005</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46254.647308750005</v>
+        <v>46255.628654224536</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -522,232 +522,232 @@
     <t>Ingenieria y diseño:,Plano Definitivos   4386  ,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
   </si>
   <si>
+    <t>1217003865116857</t>
+  </si>
+  <si>
+    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>1217003845096835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos   4386  </t>
+  </si>
+  <si>
+    <t>Plano Preliminar   4386  ,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,Check Planos   4386 </t>
+  </si>
+  <si>
+    <t>1217003865125172</t>
+  </si>
+  <si>
+    <t>1217003845116438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Plano Definitivos   4386  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Propuesta Fabricación externa  4386 ,Propuesta Mecanizado 4386 ,Propuesta Corte plasma 4386 ,propuesta Corte laser  4386 </t>
+  </si>
+  <si>
+    <t>1217003715168796</t>
+  </si>
+  <si>
+    <t>1217003715191754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  4386  </t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>1217003865213826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check pruebas FAT  4386  </t>
+  </si>
+  <si>
+    <t>1217003777524849</t>
+  </si>
+  <si>
+    <t>1217003777524862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o t 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check pruebas FAT  4386  </t>
+  </si>
+  <si>
+    <t>1217003777524875</t>
+  </si>
+  <si>
+    <t>1217003865287547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  4386 ,Control de calidad corte Laser ot  4386,Control de calidad Corte plasma  ot 4386,Recepcion corte plasma    4386,Recepcion corte laser   ot  4386  ,Control de calidad Mecanizado  ot  4386 </t>
+  </si>
+  <si>
+    <t>1217003865287559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   ot  4386  </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser ot  4386,Bodega </t>
+  </si>
+  <si>
+    <t>1217003845237249</t>
+  </si>
+  <si>
+    <t>Recepcion corte plasma    4386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma  ot 4386,Bodega </t>
+  </si>
+  <si>
+    <t>1217003845237272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  4386 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  ot  4386 </t>
+  </si>
+  <si>
+    <t>1217003688624465</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser ot  4386</t>
+  </si>
+  <si>
+    <t>1217003715316238</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma  ot 4386</t>
+  </si>
+  <si>
+    <t>1217003865302698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  ot  4386 </t>
+  </si>
+  <si>
+    <t>1217003865302721</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Preparacion materiales ot  4386  ,Armado ot  4386,Control de calidad Armado ot  4386</t>
+  </si>
+  <si>
+    <t>1217003688641445</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>1217003688641468</t>
+  </si>
+  <si>
+    <t>Armado ot  4386</t>
+  </si>
+  <si>
+    <t>1217003777634730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos   4386 ,Preparacion materiales ot  4386  </t>
+  </si>
+  <si>
+    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Armado ot  4386</t>
+  </si>
+  <si>
+    <t>1217003777635905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales ot  4386  ,Check Planos   4386 </t>
+  </si>
+  <si>
+    <t>1217003777635928</t>
+  </si>
+  <si>
+    <t>Armado ot  4386,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>1217003715350845</t>
+  </si>
+  <si>
+    <t>1217003865387632</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado ot  4386</t>
+  </si>
+  <si>
+    <t>1217003688754592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check Planos   4386 </t>
+  </si>
+  <si>
+    <t>Control de calidad Armado ot  4386,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
+    <t>1217003715436307</t>
+  </si>
+  <si>
+    <t>1217003715436330</t>
+  </si>
+  <si>
+    <t>1217003777740196</t>
+  </si>
+  <si>
+    <t>1217003978601544</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor ot 4386,Recepcion Alabe ot  4386,Recepcion Rodete ot  4386  </t>
+  </si>
+  <si>
+    <t>1217003978601556</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe ot  4386</t>
+  </si>
+  <si>
+    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Bodega:,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1217003865116857</t>
-  </si>
-  <si>
-    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>1217003845096835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos   4386  </t>
-  </si>
-  <si>
-    <t>Plano Preliminar   4386  ,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,Check Planos   4386 </t>
-  </si>
-  <si>
-    <t>1217003865125172</t>
-  </si>
-  <si>
-    <t>1217003845116438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Plano Definitivos   4386  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Propuesta Fabricación externa  4386 ,Propuesta Mecanizado 4386 ,Propuesta Corte plasma 4386 ,propuesta Corte laser  4386 </t>
-  </si>
-  <si>
-    <t>1217003715168796</t>
-  </si>
-  <si>
-    <t>1217003715191754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  4386  </t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>1217003865213826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check pruebas FAT  4386  </t>
-  </si>
-  <si>
-    <t>1217003777524849</t>
-  </si>
-  <si>
-    <t>1217003777524862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o t 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check pruebas FAT  4386  </t>
-  </si>
-  <si>
-    <t>1217003777524875</t>
-  </si>
-  <si>
-    <t>1217003865287547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  4386 ,Control de calidad corte Laser ot  4386,Control de calidad Corte plasma  ot 4386,Recepcion corte plasma    4386,Recepcion corte laser   ot  4386  ,Control de calidad Mecanizado  ot  4386 </t>
-  </si>
-  <si>
-    <t>1217003865287559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   ot  4386  </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser ot  4386,Bodega </t>
-  </si>
-  <si>
-    <t>1217003845237249</t>
-  </si>
-  <si>
-    <t>Recepcion corte plasma    4386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma  ot 4386,Bodega </t>
-  </si>
-  <si>
-    <t>1217003845237272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  4386 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  ot  4386 </t>
-  </si>
-  <si>
-    <t>1217003688624465</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser ot  4386</t>
-  </si>
-  <si>
-    <t>1217003715316238</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma  ot 4386</t>
-  </si>
-  <si>
-    <t>1217003865302698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  ot  4386 </t>
-  </si>
-  <si>
-    <t>1217003865302721</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Preparacion materiales ot  4386  ,Armado ot  4386,Control de calidad Armado ot  4386</t>
-  </si>
-  <si>
-    <t>1217003688641445</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>1217003688641468</t>
-  </si>
-  <si>
-    <t>Armado ot  4386</t>
-  </si>
-  <si>
-    <t>1217003777634730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos   4386 ,Preparacion materiales ot  4386  </t>
-  </si>
-  <si>
-    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Armado ot  4386</t>
-  </si>
-  <si>
-    <t>1217003777635905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales ot  4386  ,Check Planos   4386 </t>
-  </si>
-  <si>
-    <t>1217003777635928</t>
-  </si>
-  <si>
-    <t>Armado ot  4386,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>1217003715350845</t>
-  </si>
-  <si>
-    <t>1217003865387632</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado ot  4386</t>
-  </si>
-  <si>
-    <t>1217003688754592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Check Planos   4386 </t>
-  </si>
-  <si>
-    <t>Control de calidad Armado ot  4386,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
-  </si>
-  <si>
-    <t>1217003715436307</t>
-  </si>
-  <si>
-    <t>1217003715436330</t>
-  </si>
-  <si>
-    <t>1217003777740196</t>
-  </si>
-  <si>
-    <t>1217003978601544</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor ot 4386,Recepcion Alabe ot  4386,Recepcion Rodete ot  4386  </t>
-  </si>
-  <si>
-    <t>1217003978601556</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe ot  4386</t>
-  </si>
-  <si>
-    <t>ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Bodega:,ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4</t>
   </si>
   <si>
     <t>1217003845432751</t>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46233.646022581015</v>
+        <v>46261.48903378472</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>137</v>
@@ -3722,9 +3722,11 @@
       <c r="B39" s="9">
         <v>46232.83590302084</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46261.489026967596</v>
+      </c>
       <c r="D39" s="9">
-        <v>46260.68251333333</v>
+        <v>46261.48904716435</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>140</v>
@@ -3772,15 +3774,15 @@
         <v>46</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>145</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46232.83591185186</v>
@@ -3792,16 +3794,16 @@
         <v>46260.67723627315</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -3835,17 +3837,17 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591513889</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46260.67982575232</v>
+        <v>46261.489034375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3875,10 +3877,10 @@
         <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46274</v>
@@ -3898,26 +3900,26 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83592324074</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46233.65265393518</v>
+        <v>46261.48903494213</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46268</v>
@@ -3935,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3951,7 +3953,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592622685</v>
@@ -3967,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I43" s="9">
         <v>46275</v>
@@ -3991,10 +3993,10 @@
         <v>137</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="Q43" s="9">
         <v>46275</v>
@@ -4014,7 +4016,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83594902778</v>
@@ -4024,16 +4026,16 @@
         <v>46233.65294082176</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>46275</v>
@@ -4054,7 +4056,7 @@
         <v>65</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>65</v>
@@ -4067,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83595255787</v>
@@ -4077,16 +4079,16 @@
         <v>46260.679872256944</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I45" s="9">
         <v>46356</v>
@@ -4107,7 +4109,7 @@
         <v>137</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>137</v>
@@ -4130,7 +4132,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83600618056</v>
@@ -4140,16 +4142,16 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46356</v>
@@ -4167,13 +4169,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4183,7 +4185,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83600939815</v>
@@ -4193,16 +4195,16 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I47" s="9">
         <v>46356</v>
@@ -4220,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4236,7 +4238,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83601267361</v>
@@ -4246,16 +4248,16 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4273,13 +4275,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4289,7 +4291,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B49" s="9">
         <v>46232.83601601852</v>
@@ -4299,16 +4301,16 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4326,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4342,7 +4344,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83611833333</v>
@@ -4352,7 +4354,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4376,7 +4378,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4389,7 +4391,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B51" s="9">
         <v>46232.836122465276</v>
@@ -4399,16 +4401,16 @@
         <v>46260.67989972222</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I51" s="9">
         <v>46293</v>
@@ -4426,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4452,7 +4454,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83612731482</v>
@@ -4462,16 +4464,16 @@
         <v>46260.679925335644</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I52" s="5">
         <v>46293</v>
@@ -4489,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4515,7 +4517,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46232.83613222222</v>
@@ -4525,16 +4527,16 @@
         <v>46260.679949259254</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I53" s="9">
         <v>46293</v>
@@ -4552,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>106</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4578,7 +4580,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46232.836136909726</v>
@@ -4588,7 +4590,7 @@
         <v>46260.68020320602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4615,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q54" s="5">
         <v>46295</v>
@@ -4641,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83614177084</v>
@@ -4651,7 +4653,7 @@
         <v>46260.6802031713</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4678,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q55" s="9">
         <v>46295</v>
@@ -4704,7 +4706,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83614663195</v>
@@ -4714,7 +4716,7 @@
         <v>46260.68020337963</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4741,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q56" s="5">
         <v>46295</v>
@@ -4767,7 +4769,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83615094908</v>
@@ -4777,7 +4779,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4801,7 +4803,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4814,7 +4816,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83615418982</v>
@@ -4830,10 +4832,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I58" s="5">
         <v>46296</v>
@@ -4851,13 +4853,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="5">
         <v>46304</v>
@@ -4877,7 +4879,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83616251158</v>
@@ -4887,16 +4889,16 @@
         <v>46260.680265891206</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I59" s="9">
         <v>46307</v>
@@ -4914,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q59" s="9">
         <v>46324</v>
@@ -4940,7 +4942,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83619825232</v>
@@ -4950,16 +4952,16 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I60" s="5">
         <v>46307</v>
@@ -4977,13 +4979,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4993,7 +4995,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B61" s="9">
         <v>46232.8362028125</v>
@@ -5003,16 +5005,16 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I61" s="9">
         <v>46307</v>
@@ -5030,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5046,7 +5048,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83620730324</v>
@@ -5056,16 +5058,16 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46307</v>
@@ -5083,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5099,7 +5101,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83621217593</v>
@@ -5109,16 +5111,16 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I63" s="9">
         <v>46307</v>
@@ -5136,13 +5138,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5152,7 +5154,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836342152776</v>
@@ -5162,7 +5164,7 @@
         <v>46260.68039708333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5189,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q64" s="5">
         <v>46328</v>
@@ -5215,7 +5217,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83637209491</v>
@@ -5225,7 +5227,7 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5252,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5268,7 +5270,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46232.836376666666</v>
@@ -5278,7 +5280,7 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5305,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5321,7 +5323,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B67" s="9">
         <v>46232.836381319445</v>
@@ -5331,7 +5333,7 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5358,13 +5360,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5374,7 +5376,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83638501157</v>
@@ -5384,7 +5386,7 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5411,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5427,7 +5429,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B69" s="9">
         <v>46232.836502499995</v>
@@ -5437,7 +5439,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5461,7 +5463,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5474,7 +5476,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83650636574</v>
@@ -5484,16 +5486,16 @@
         <v>46260.68082252315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I70" s="5">
         <v>46239</v>
@@ -5511,13 +5513,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q70" s="5">
         <v>46240</v>
@@ -5532,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5553,10 +5555,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I71" s="9">
         <v>46239</v>
@@ -5574,13 +5576,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q71" s="9">
         <v>46240</v>
@@ -5616,10 +5618,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5637,7 +5639,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>132</v>
@@ -5750,7 +5752,7 @@
         <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>227</v>
@@ -5783,7 +5785,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5813,7 +5815,7 @@
         <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>232</v>
@@ -5836,7 +5838,7 @@
         <v>46260.680678715275</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5866,7 +5868,7 @@
         <v>230</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>232</v>
@@ -5889,7 +5891,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5919,7 +5921,7 @@
         <v>230</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>232</v>
@@ -5942,7 +5944,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5972,7 +5974,7 @@
         <v>230</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>232</v>
@@ -6025,7 +6027,7 @@
         <v>227</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>227</v>
@@ -6058,7 +6060,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6111,7 +6113,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6164,7 +6166,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6217,7 +6219,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6300,7 +6302,7 @@
         <v>227</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>227</v>
@@ -6333,7 +6335,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6386,7 +6388,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6439,7 +6441,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6492,7 +6494,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6575,7 +6577,7 @@
         <v>227</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>227</v>
@@ -6608,7 +6610,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6638,7 +6640,7 @@
         <v>253</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>255</v>
@@ -6661,7 +6663,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6691,7 +6693,7 @@
         <v>253</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>255</v>
@@ -6714,7 +6716,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6744,7 +6746,7 @@
         <v>253</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>255</v>
@@ -6767,7 +6769,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6797,7 +6799,7 @@
         <v>253</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>255</v>
@@ -6850,10 +6852,10 @@
         <v>227</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q94" s="5">
         <v>46352</v>
@@ -6883,7 +6885,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6913,7 +6915,7 @@
         <v>260</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>260</v>
@@ -6936,7 +6938,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6966,7 +6968,7 @@
         <v>260</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>260</v>
@@ -6989,7 +6991,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7019,7 +7021,7 @@
         <v>260</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>260</v>
@@ -7042,7 +7044,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7072,7 +7074,7 @@
         <v>260</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>260</v>
@@ -7125,7 +7127,7 @@
         <v>227</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7158,7 +7160,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7211,7 +7213,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7264,7 +7266,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7317,7 +7319,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7433,7 +7435,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7463,7 +7465,7 @@
         <v>273</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>276</v>
@@ -7486,7 +7488,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7516,7 +7518,7 @@
         <v>273</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>276</v>
@@ -7569,7 +7571,7 @@
         <v>273</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>276</v>
@@ -7592,7 +7594,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7622,7 +7624,7 @@
         <v>273</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>276</v>
@@ -7722,7 +7724,7 @@
         <v>282</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>288</v>
@@ -7755,7 +7757,7 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7785,7 +7787,7 @@
         <v>285</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>290</v>
@@ -7808,7 +7810,7 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7838,7 +7840,7 @@
         <v>285</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>290</v>
@@ -7861,7 +7863,7 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7914,7 +7916,7 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7944,7 +7946,7 @@
         <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>290</v>
@@ -8030,7 +8032,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8060,7 +8062,7 @@
         <v>295</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>298</v>
@@ -8083,7 +8085,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8113,7 +8115,7 @@
         <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>298</v>
@@ -8136,7 +8138,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8166,7 +8168,7 @@
         <v>295</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>298</v>
@@ -8189,7 +8191,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8219,7 +8221,7 @@
         <v>295</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>298</v>
@@ -8248,10 +8250,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I120" s="5">
         <v>46363</v>
@@ -8272,7 +8274,7 @@
         <v>282</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>282</v>
@@ -8305,16 +8307,16 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I121" s="9">
         <v>46363</v>
@@ -8335,7 +8337,7 @@
         <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>305</v>
@@ -8358,16 +8360,16 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I122" s="5">
         <v>46363</v>
@@ -8388,7 +8390,7 @@
         <v>303</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>307</v>
@@ -8411,16 +8413,16 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I123" s="9">
         <v>46363</v>
@@ -8441,7 +8443,7 @@
         <v>303</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>307</v>
@@ -8464,16 +8466,16 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I124" s="5">
         <v>46363</v>
@@ -8494,7 +8496,7 @@
         <v>303</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>305</v>
@@ -8523,10 +8525,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I125" s="9">
         <v>46364</v>
@@ -8547,7 +8549,7 @@
         <v>282</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>312</v>
@@ -8580,16 +8582,16 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I126" s="5">
         <v>46364</v>
@@ -8610,7 +8612,7 @@
         <v>311</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>311</v>
@@ -8633,16 +8635,16 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I127" s="9">
         <v>46364</v>
@@ -8663,7 +8665,7 @@
         <v>311</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>311</v>
@@ -8686,16 +8688,16 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I128" s="5">
         <v>46364</v>
@@ -8716,7 +8718,7 @@
         <v>311</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>311</v>
@@ -8739,16 +8741,16 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I129" s="9">
         <v>46364</v>
@@ -8769,7 +8771,7 @@
         <v>311</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>311</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="327">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -544,6 +544,9 @@
   </si>
   <si>
     <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,Check Planos   4386 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217003865125172</t>
@@ -3844,7 +3847,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46261.489034375</v>
+        <v>46267.201737337964</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>150</v>
@@ -3888,8 +3891,8 @@
       <c r="R41" s="9">
         <v>46268</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>33</v>
+      <c r="S41" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83592324074</v>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592622685</v>
@@ -3993,10 +3996,10 @@
         <v>137</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9">
         <v>46275</v>
@@ -4016,7 +4019,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83594902778</v>
@@ -4069,7 +4072,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83595255787</v>
@@ -4079,16 +4082,16 @@
         <v>46260.679872256944</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9">
         <v>46356</v>
@@ -4109,7 +4112,7 @@
         <v>137</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>137</v>
@@ -4132,7 +4135,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83600618056</v>
@@ -4148,10 +4151,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46356</v>
@@ -4169,13 +4172,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4185,7 +4188,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83600939815</v>
@@ -4201,10 +4204,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I47" s="9">
         <v>46356</v>
@@ -4222,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83601267361</v>
@@ -4254,10 +4257,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4275,13 +4278,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4291,7 +4294,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" s="9">
         <v>46232.83601601852</v>
@@ -4307,10 +4310,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4328,13 +4331,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4344,7 +4347,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83611833333</v>
@@ -4354,7 +4357,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4378,7 +4381,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4391,7 +4394,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9">
         <v>46232.836122465276</v>
@@ -4401,16 +4404,16 @@
         <v>46260.67989972222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I51" s="9">
         <v>46293</v>
@@ -4428,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4454,7 +4457,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83612731482</v>
@@ -4464,16 +4467,16 @@
         <v>46260.679925335644</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I52" s="5">
         <v>46293</v>
@@ -4491,13 +4494,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" s="9">
         <v>46232.83613222222</v>
@@ -4527,16 +4530,16 @@
         <v>46260.679949259254</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I53" s="9">
         <v>46293</v>
@@ -4554,13 +4557,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>106</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46232.836136909726</v>
@@ -4590,7 +4593,7 @@
         <v>46260.68020320602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4617,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="5">
         <v>46295</v>
@@ -4643,7 +4646,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83614177084</v>
@@ -4653,7 +4656,7 @@
         <v>46260.6802031713</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4680,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="9">
         <v>46295</v>
@@ -4706,7 +4709,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83614663195</v>
@@ -4716,7 +4719,7 @@
         <v>46260.68020337963</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4743,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56" s="5">
         <v>46295</v>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83615094908</v>
@@ -4779,7 +4782,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4803,7 +4806,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83615418982</v>
@@ -4832,10 +4835,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I58" s="5">
         <v>46296</v>
@@ -4853,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="5">
         <v>46304</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83616251158</v>
@@ -4889,16 +4892,16 @@
         <v>46260.680265891206</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I59" s="9">
         <v>46307</v>
@@ -4916,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59" s="9">
         <v>46324</v>
@@ -4942,7 +4945,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83619825232</v>
@@ -4958,10 +4961,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I60" s="5">
         <v>46307</v>
@@ -4979,13 +4982,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4995,7 +4998,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46232.8362028125</v>
@@ -5011,10 +5014,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I61" s="9">
         <v>46307</v>
@@ -5032,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83620730324</v>
@@ -5064,10 +5067,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46307</v>
@@ -5085,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5101,7 +5104,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83621217593</v>
@@ -5117,10 +5120,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I63" s="9">
         <v>46307</v>
@@ -5138,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5154,7 +5157,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836342152776</v>
@@ -5164,7 +5167,7 @@
         <v>46260.68039708333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5191,13 +5194,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q64" s="5">
         <v>46328</v>
@@ -5217,7 +5220,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83637209491</v>
@@ -5254,13 +5257,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5270,7 +5273,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46232.836376666666</v>
@@ -5307,13 +5310,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B67" s="9">
         <v>46232.836381319445</v>
@@ -5360,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5376,7 +5379,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83638501157</v>
@@ -5413,13 +5416,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5429,7 +5432,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B69" s="9">
         <v>46232.836502499995</v>
@@ -5439,7 +5442,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5463,7 +5466,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5476,7 +5479,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83650636574</v>
@@ -5486,16 +5489,16 @@
         <v>46260.68082252315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I70" s="5">
         <v>46239</v>
@@ -5513,13 +5516,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46240</v>
@@ -5534,12 +5537,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B71" s="9">
         <v>46232.836519247685</v>
@@ -5549,16 +5552,16 @@
         <v>46260.68090866898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I71" s="9">
         <v>46239</v>
@@ -5576,13 +5579,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71" s="9">
         <v>46240</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B72" s="5">
         <v>46232.83652788194</v>
@@ -5612,16 +5615,16 @@
         <v>46260.680964652776</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5639,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>132</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q72" s="5">
         <v>46344</v>
@@ -5665,7 +5668,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B73" s="9">
         <v>46232.83654054398</v>
@@ -5675,7 +5678,7 @@
         <v>46233.645743333334</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5699,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5712,7 +5715,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B74" s="5">
         <v>46232.83654375</v>
@@ -5722,7 +5725,7 @@
         <v>46260.68063219907</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5749,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q74" s="5">
         <v>46346</v>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B75" s="9">
         <v>46232.836570162035</v>
@@ -5812,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" s="5">
         <v>46232.83657339121</v>
@@ -5865,13 +5868,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5881,7 +5884,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B77" s="9">
         <v>46232.83657665509</v>
@@ -5918,13 +5921,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5934,7 +5937,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B78" s="5">
         <v>46232.83658011574</v>
@@ -5971,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B79" s="9">
         <v>46232.83664298611</v>
@@ -5997,7 +6000,7 @@
         <v>46260.681952962965</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6024,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q79" s="9">
         <v>46349</v>
@@ -6050,7 +6053,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B80" s="5">
         <v>46232.8367334375</v>
@@ -6087,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6103,7 +6106,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B81" s="9">
         <v>46232.83673865741</v>
@@ -6140,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B82" s="5">
         <v>46232.83674337963</v>
@@ -6193,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6209,7 +6212,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B83" s="9">
         <v>46232.83674840278</v>
@@ -6246,13 +6249,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B84" s="5">
         <v>46232.836891377316</v>
@@ -6272,7 +6275,7 @@
         <v>46260.68198707176</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6299,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="5">
         <v>46350</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B85" s="9">
         <v>46232.836924375</v>
@@ -6362,13 +6365,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6378,7 +6381,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B86" s="5">
         <v>46232.836927488424</v>
@@ -6415,13 +6418,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6431,7 +6434,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B87" s="9">
         <v>46232.836930474536</v>
@@ -6468,13 +6471,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6484,7 +6487,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="5">
         <v>46232.836933530096</v>
@@ -6521,13 +6524,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6537,7 +6540,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="9">
         <v>46232.836990428244</v>
@@ -6547,7 +6550,7 @@
         <v>46260.68201387732</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6574,13 +6577,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q89" s="9">
         <v>46351</v>
@@ -6600,7 +6603,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B90" s="5">
         <v>46232.83702368056</v>
@@ -6637,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6653,7 +6656,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B91" s="9">
         <v>46232.837026863424</v>
@@ -6690,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6706,7 +6709,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B92" s="5">
         <v>46232.83702931713</v>
@@ -6743,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6759,7 +6762,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B93" s="9">
         <v>46232.83703243056</v>
@@ -6796,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6812,7 +6815,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B94" s="5">
         <v>46232.83713237269</v>
@@ -6822,7 +6825,7 @@
         <v>46260.682038240746</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6849,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q94" s="5">
         <v>46352</v>
@@ -6875,7 +6878,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B95" s="9">
         <v>46232.83715663194</v>
@@ -6912,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6928,7 +6931,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B96" s="5">
         <v>46232.83715961805</v>
@@ -6965,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6981,7 +6984,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B97" s="9">
         <v>46232.83716207176</v>
@@ -7018,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7034,7 +7037,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="5">
         <v>46232.837165324076</v>
@@ -7071,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7087,7 +7090,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B99" s="9">
         <v>46232.837259120366</v>
@@ -7097,7 +7100,7 @@
         <v>46260.68206168982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7124,10 +7127,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7150,7 +7153,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B100" s="5">
         <v>46232.837293495366</v>
@@ -7187,13 +7190,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7203,7 +7206,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B101" s="9">
         <v>46232.83729747686</v>
@@ -7240,13 +7243,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7256,7 +7259,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B102" s="5">
         <v>46232.83730121527</v>
@@ -7293,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7309,7 +7312,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B103" s="9">
         <v>46232.83730554398</v>
@@ -7346,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7362,7 +7365,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B104" s="5">
         <v>46232.83737395833</v>
@@ -7372,7 +7375,7 @@
         <v>46260.68208619213</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7399,10 +7402,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>26</v>
@@ -7425,7 +7428,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B105" s="9">
         <v>46232.83744990741</v>
@@ -7462,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7478,7 +7481,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B106" s="5">
         <v>46232.83745327547</v>
@@ -7515,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7531,7 +7534,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="9">
         <v>46232.837456712965</v>
@@ -7541,7 +7544,7 @@
         <v>46233.65578273148</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7568,13 +7571,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7584,7 +7587,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>46232.83746033565</v>
@@ -7621,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7637,7 +7640,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B109" s="9">
         <v>46232.837520092595</v>
@@ -7647,7 +7650,7 @@
         <v>46233.64911908565</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>25</v>
@@ -7671,7 +7674,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7684,7 +7687,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B110" s="5">
         <v>46232.837524166665</v>
@@ -7694,16 +7697,16 @@
         <v>46260.68212885417</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I110" s="5">
         <v>46359</v>
@@ -7721,13 +7724,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q110" s="5">
         <v>46359</v>
@@ -7747,7 +7750,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B111" s="9">
         <v>46232.83755571759</v>
@@ -7763,10 +7766,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I111" s="9">
         <v>46359</v>
@@ -7784,13 +7787,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B112" s="5">
         <v>46232.837559548614</v>
@@ -7816,10 +7819,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I112" s="5">
         <v>46359</v>
@@ -7837,13 +7840,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7853,7 +7856,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B113" s="9">
         <v>46232.83756364584</v>
@@ -7869,10 +7872,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I113" s="9">
         <v>46359</v>
@@ -7890,13 +7893,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7906,7 +7909,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B114" s="5">
         <v>46232.83756778935</v>
@@ -7922,10 +7925,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I114" s="5">
         <v>46359</v>
@@ -7943,13 +7946,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7959,7 +7962,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B115" s="9">
         <v>46232.83768009259</v>
@@ -7969,7 +7972,7 @@
         <v>46260.68216930555</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7996,10 +7999,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B116" s="5">
         <v>46232.837703680554</v>
@@ -8059,13 +8062,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8075,7 +8078,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B117" s="9">
         <v>46232.837707175924</v>
@@ -8112,13 +8115,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8128,7 +8131,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B118" s="5">
         <v>46232.837710555556</v>
@@ -8165,13 +8168,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8181,7 +8184,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B119" s="9">
         <v>46232.837713981484</v>
@@ -8218,13 +8221,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8234,7 +8237,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B120" s="5">
         <v>46232.837813125</v>
@@ -8244,16 +8247,16 @@
         <v>46260.68218884259</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I120" s="5">
         <v>46363</v>
@@ -8271,13 +8274,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q120" s="5">
         <v>46363</v>
@@ -8297,7 +8300,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B121" s="9">
         <v>46232.83784550926</v>
@@ -8313,10 +8316,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I121" s="9">
         <v>46363</v>
@@ -8334,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8350,7 +8353,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B122" s="5">
         <v>46232.837850254626</v>
@@ -8366,10 +8369,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I122" s="5">
         <v>46363</v>
@@ -8387,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8403,7 +8406,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B123" s="9">
         <v>46232.83785502314</v>
@@ -8419,10 +8422,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I123" s="9">
         <v>46363</v>
@@ -8440,13 +8443,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8456,7 +8459,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B124" s="5">
         <v>46232.83785935185</v>
@@ -8472,10 +8475,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I124" s="5">
         <v>46363</v>
@@ -8493,13 +8496,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8509,7 +8512,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B125" s="9">
         <v>46232.837973483794</v>
@@ -8519,16 +8522,16 @@
         <v>46260.682238113426</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I125" s="9">
         <v>46364</v>
@@ -8546,13 +8549,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q125" s="9">
         <v>46364</v>
@@ -8572,7 +8575,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B126" s="5">
         <v>46232.838005439815</v>
@@ -8588,10 +8591,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I126" s="5">
         <v>46364</v>
@@ -8609,13 +8612,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8625,7 +8628,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B127" s="9">
         <v>46232.838009259256</v>
@@ -8641,10 +8644,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I127" s="9">
         <v>46364</v>
@@ -8662,13 +8665,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8678,7 +8681,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B128" s="5">
         <v>46232.83801302083</v>
@@ -8694,10 +8697,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I128" s="5">
         <v>46364</v>
@@ -8715,13 +8718,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8731,7 +8734,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B129" s="9">
         <v>46232.83801685185</v>
@@ -8747,10 +8750,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I129" s="9">
         <v>46364</v>
@@ -8768,13 +8771,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8784,7 +8787,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B130" s="5">
         <v>46232.83807947917</v>
@@ -8794,7 +8797,7 @@
         <v>46233.65049251157</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>25</v>
@@ -8818,7 +8821,7 @@
         <v>26</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>26</v>
@@ -8831,7 +8834,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B131" s="9">
         <v>46232.83808368056</v>
@@ -8841,16 +8844,16 @@
         <v>46260.68180542824</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I131" s="9">
         <v>46365</v>
@@ -8868,13 +8871,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q131" s="9">
         <v>46373</v>
@@ -8894,7 +8897,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B132" s="5">
         <v>46232.83812608796</v>
@@ -8904,16 +8907,16 @@
         <v>46260.68180643518</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I132" s="5">
         <v>46365</v>
@@ -8931,13 +8934,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q132" s="5">
         <v>46373</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -3963,7 +3963,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46260.68039732639</v>
+        <v>46268.20829188658</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>65</v>
@@ -4007,8 +4007,8 @@
       <c r="R43" s="9">
         <v>46275</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>33</v>
+      <c r="S43" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2064,7 +2064,7 @@
         <v>46252.60046905093</v>
       </c>
       <c r="D10" s="5">
-        <v>46260.67900259259</v>
+        <v>46269.8968203588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>42</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -288,6 +288,9 @@
     <t>Generación OC corte laser   ot 4385- 4386,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -544,9 +547,6 @@
   </si>
   <si>
     <t xml:space="preserve">ot 4386  - VENTILADORES 90KCFMx3"CA - ZVN 1-16-55/4,Ingenieria y diseño:,Check Planos   4386 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217003865125172</t>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46252.60261606482</v>
+        <v>46272.16623265046</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2393,29 +2393,29 @@
       <c r="R15" s="9">
         <v>46276</v>
       </c>
-      <c r="S15" s="7" t="s">
-        <v>33</v>
+      <c r="S15" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>46232.83579084491</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46252.602689189815</v>
+        <v>46272.16623270833</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2448,7 +2448,7 @@
         <v>65</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46279</v>
@@ -2456,29 +2456,29 @@
       <c r="R16" s="5">
         <v>46276</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>33</v>
+      <c r="S16" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="9">
         <v>46232.83579519676</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46252.60271420139</v>
+        <v>46272.16623267361</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2511,7 +2511,7 @@
         <v>65</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46279</v>
@@ -2519,29 +2519,29 @@
       <c r="R17" s="9">
         <v>46276</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>33</v>
+      <c r="S17" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46232.83579891204</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46252.602754872685</v>
+        <v>46272.16623268518</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2574,7 +2574,7 @@
         <v>65</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46279</v>
@@ -2582,19 +2582,19 @@
       <c r="R18" s="5">
         <v>46276</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+      <c r="S18" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="9">
         <v>46232.8586305787</v>
@@ -2639,7 +2639,7 @@
         <v>44</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="9">
         <v>46239</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46232.83564635417</v>
@@ -2669,7 +2669,7 @@
         <v>46233.639479722224</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2693,7 +2693,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="9">
         <v>46232.83580497685</v>
@@ -2716,16 +2716,16 @@
         <v>46252.60280438657</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="9">
         <v>46280</v>
@@ -2743,13 +2743,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q21" s="9">
         <v>46290</v>
@@ -2764,12 +2764,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46232.835810578705</v>
@@ -2779,16 +2779,16 @@
         <v>46233.651251539355</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46280</v>
@@ -2806,13 +2806,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2823,12 +2823,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46232.83581497685</v>
@@ -2838,16 +2838,16 @@
         <v>46233.651247037036</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" s="9">
         <v>46282</v>
@@ -2865,13 +2865,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2882,12 +2882,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46232.835819618056</v>
@@ -2897,16 +2897,16 @@
         <v>46252.602819155094</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46280</v>
@@ -2924,10 +2924,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2945,12 +2945,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46232.83582385417</v>
@@ -2960,16 +2960,16 @@
         <v>46233.651424247684</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I25" s="9">
         <v>46280</v>
@@ -2987,13 +2987,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46232.835827523144</v>
@@ -3013,16 +3013,16 @@
         <v>46233.651529675924</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46282</v>
@@ -3040,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46232.83583092593</v>
@@ -3066,16 +3066,16 @@
         <v>46252.602839178246</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" s="9">
         <v>46280</v>
@@ -3093,10 +3093,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3114,12 +3114,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46232.83583467593</v>
@@ -3129,16 +3129,16 @@
         <v>46240.823460775464</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46280</v>
@@ -3156,13 +3156,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46232.83583809028</v>
@@ -3182,16 +3182,16 @@
         <v>46240.82345635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" s="9">
         <v>46282</v>
@@ -3209,13 +3209,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46232.835841458334</v>
@@ -3235,16 +3235,16 @@
         <v>46252.602874247685</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46280</v>
@@ -3262,10 +3262,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3283,12 +3283,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="9">
         <v>46232.83584547453</v>
@@ -3298,16 +3298,16 @@
         <v>46255.628654224536</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I31" s="9">
         <v>46280</v>
@@ -3325,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46232.83584972222</v>
@@ -3351,16 +3351,16 @@
         <v>46233.652321284724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46290</v>
@@ -3378,13 +3378,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46232.83585321759</v>
@@ -3404,16 +3404,16 @@
         <v>46233.65237416667</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="9">
         <v>46321</v>
@@ -3431,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46232.85014579861</v>
@@ -3457,16 +3457,16 @@
         <v>46252.60289347223</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46240</v>
@@ -3484,10 +3484,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3505,12 +3505,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46232.85120104167</v>
@@ -3522,16 +3522,16 @@
         <v>46233.907791053236</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46240</v>
@@ -3549,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46232.85127679398</v>
@@ -3575,16 +3575,16 @@
         <v>46233.90779653935</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46259</v>
@@ -3602,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3618,7 +3618,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46232.85132364584</v>
@@ -3630,16 +3630,16 @@
         <v>46233.90783645833</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46230</v>
@@ -3657,10 +3657,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46232.83589858796</v>
@@ -3683,7 +3683,7 @@
         <v>46261.48903378472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3707,7 +3707,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" s="9">
         <v>46232.83590302084</v>
@@ -3732,16 +3732,16 @@
         <v>46261.48904716435</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3759,13 +3759,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9">
         <v>46245</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46232.83591185186</v>
@@ -3797,16 +3797,16 @@
         <v>46260.67723627315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -3824,13 +3824,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591513889</v>
@@ -3850,16 +3850,16 @@
         <v>46267.201737337964</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I41" s="9">
         <v>46268</v>
@@ -3877,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46274</v>
@@ -3892,13 +3892,13 @@
         <v>46268</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3913,16 +3913,16 @@
         <v>46261.48903494213</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46268</v>
@@ -3940,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3972,10 +3972,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I43" s="9">
         <v>46275</v>
@@ -3993,7 +3993,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>156</v>
@@ -4008,13 +4008,13 @@
         <v>46275</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4029,16 +4029,16 @@
         <v>46233.65294082176</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>46275</v>
@@ -4059,7 +4059,7 @@
         <v>65</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>65</v>
@@ -4109,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q45" s="9">
         <v>46356</v>
@@ -4130,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4145,7 +4145,7 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4175,7 +4175,7 @@
         <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>165</v>
@@ -4198,7 +4198,7 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4228,7 +4228,7 @@
         <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>165</v>
@@ -4251,7 +4251,7 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4281,7 +4281,7 @@
         <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>168</v>
@@ -4304,7 +4304,7 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4334,7 +4334,7 @@
         <v>160</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>165</v>
@@ -4434,7 +4434,7 @@
         <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>177</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4497,7 +4497,7 @@
         <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>180</v>
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4560,7 +4560,7 @@
         <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>183</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4599,10 +4599,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" s="5">
         <v>46295</v>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4662,10 +4662,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4725,10 +4725,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I56" s="5">
         <v>46295</v>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4829,7 +4829,7 @@
         <v>46260.68026579861</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4859,7 +4859,7 @@
         <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>196</v>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4955,7 +4955,7 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5008,7 +5008,7 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5061,7 +5061,7 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5114,7 +5114,7 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5173,10 +5173,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I64" s="5">
         <v>46325</v>
@@ -5215,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5230,16 +5230,16 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I65" s="9">
         <v>46325</v>
@@ -5283,16 +5283,16 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I66" s="5">
         <v>46325</v>
@@ -5336,16 +5336,16 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I67" s="9">
         <v>46325</v>
@@ -5366,7 +5366,7 @@
         <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>211</v>
@@ -5389,16 +5389,16 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I68" s="5">
         <v>46325</v>
@@ -5600,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5645,7 +5645,7 @@
         <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>226</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5788,7 +5788,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5818,7 +5818,7 @@
         <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>233</v>
@@ -5841,7 +5841,7 @@
         <v>46260.680678715275</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5871,7 +5871,7 @@
         <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>233</v>
@@ -5894,7 +5894,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5924,7 +5924,7 @@
         <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>233</v>
@@ -5947,7 +5947,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5977,7 +5977,7 @@
         <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>233</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6063,7 +6063,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6116,7 +6116,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6169,7 +6169,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6222,7 +6222,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6391,7 +6391,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6444,7 +6444,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6497,7 +6497,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6598,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6643,7 +6643,7 @@
         <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>256</v>
@@ -6666,7 +6666,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6696,7 +6696,7 @@
         <v>254</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>256</v>
@@ -6719,7 +6719,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6749,7 +6749,7 @@
         <v>254</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>256</v>
@@ -6772,7 +6772,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6802,7 +6802,7 @@
         <v>254</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>256</v>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6888,7 +6888,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6918,7 +6918,7 @@
         <v>261</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>261</v>
@@ -6941,7 +6941,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6971,7 +6971,7 @@
         <v>261</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>261</v>
@@ -6994,7 +6994,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7024,7 +7024,7 @@
         <v>261</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>261</v>
@@ -7047,7 +7047,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7077,7 +7077,7 @@
         <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>261</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7163,7 +7163,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7216,7 +7216,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7269,7 +7269,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7322,7 +7322,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7438,7 +7438,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7468,7 +7468,7 @@
         <v>274</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>277</v>
@@ -7491,7 +7491,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7521,7 +7521,7 @@
         <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>277</v>
@@ -7574,7 +7574,7 @@
         <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>277</v>
@@ -7597,7 +7597,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7627,7 +7627,7 @@
         <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>277</v>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -7760,7 +7760,7 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7790,7 +7790,7 @@
         <v>286</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>291</v>
@@ -7813,7 +7813,7 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7843,7 +7843,7 @@
         <v>286</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>291</v>
@@ -7866,7 +7866,7 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7919,7 +7919,7 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7949,7 +7949,7 @@
         <v>286</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>291</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8035,7 +8035,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8065,7 +8065,7 @@
         <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>299</v>
@@ -8088,7 +8088,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8118,7 +8118,7 @@
         <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>299</v>
@@ -8141,7 +8141,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8171,7 +8171,7 @@
         <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>299</v>
@@ -8194,7 +8194,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8224,7 +8224,7 @@
         <v>296</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>299</v>
@@ -8295,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8310,7 +8310,7 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>304</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>306</v>
@@ -8363,7 +8363,7 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8393,7 +8393,7 @@
         <v>304</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>308</v>
@@ -8416,7 +8416,7 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8446,7 +8446,7 @@
         <v>304</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>308</v>
@@ -8469,7 +8469,7 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8499,7 +8499,7 @@
         <v>304</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>306</v>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8585,7 +8585,7 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8615,7 +8615,7 @@
         <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>312</v>
@@ -8638,7 +8638,7 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8668,7 +8668,7 @@
         <v>312</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>312</v>
@@ -8691,7 +8691,7 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8721,7 +8721,7 @@
         <v>312</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>312</v>
@@ -8744,7 +8744,7 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8774,7 +8774,7 @@
         <v>312</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>312</v>
@@ -8892,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -8955,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="U132" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46267.201737337964</v>
+        <v>46274.16880900463</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>151</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46261.48903494213</v>
+        <v>46274.16881178241</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>147</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46274.16880900463</v>
+        <v>46275.162032314816</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>151</v>
@@ -3891,8 +3891,8 @@
       <c r="R41" s="9">
         <v>46268</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>67</v>
+      <c r="S41" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46268.20829188658</v>
+        <v>46275.168794363424</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>65</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46233.65294082176</v>
+        <v>46275.1687925</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>147</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -3963,7 +3963,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46275.168794363424</v>
+        <v>46276.16113916667</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>65</v>
@@ -4007,8 +4007,8 @@
       <c r="R43" s="9">
         <v>46275</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>67</v>
+      <c r="S43" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
